--- a/data_extactor/batch_10_fa/batch_0006_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0006_fa.xlsx
@@ -493,12 +493,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fitness and Wellness Coordinators (هماهنگ‌کنندگان تناسب اندام و سلامتی)</t>
+          <t>هماهنگ‌کنندگان تناسب اندام و سلامتی (Fitness and Wellness Coordinators)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Clinical and Wellness Programs Manager | Fitness Center Manager | Fitness Coordinator | Fitness Director | Fitness and Wellness Coordinator | Fitness and Wellness Director | Group Fitness Manager (GFM) | Wellness Director | Wellness Programs Director | Wellness and Coaching Manager</t>
+          <t>مدیر برنامه‌های بالینی و سلامتی | مدیر باشگاه تناسب اندام | هماهنگ‌کننده تناسب اندام | مدیر ارشد تناسب اندام | هماهنگ‌کننده تناسب اندام و سلامتی | مدیر ارشد تناسب اندام و سلامتی | مدیر تناسب اندام گروهی (GFM) | مدیر ارشد سلامتی | مدیر ارشد برنامه‌های سلامتی | مدیر سلامتی و مربیگری</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Writing | Monitoring | Learning Strategies | Active Learning</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Customer and Personal Service | Education and Training | Administration and Management | English Language | Administrative | Sales and Marketing | Personnel and Human Resources | Psychology | Communications and Media</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | زبان انگلیسی | اداری | فروش و بازاریابی | پرسنل و منابع انسانی | روان‌شناسی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Oral Expression | Deductive Reasoning | Written Comprehension | Speech Recognition | Speech Clarity | Written Expression | Problem Sensitivity | Inductive Reasoning | Information Ordering | Near Vision | Fluency of Ideas | Category Flexibility | Originality | Far Vision | Trunk Strength | Memorization</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | بینایی دور | قدرت تنه | حفظ کردن</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Contact With Others | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Health and Safety of Other Workers | Deal With External Customers or the Public in General | Work Outcomes and Results of Other Workers</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Community Health Workers | Dietetic Technicians | Dietitians and Nutritionists | Education and Childcare Administrators, Preschool and Daycare | Exercise Physiologists | Exercise Trainers and Group Fitness Instructors | First-Line Supervisors of Personal Service Workers | Health Education Specialists | Management Analysts | Medical and Health Services Managers | Mental Health Counselors | Occupational Therapy Aides | Recreation Workers | Recreation and Fitness Studies Teachers, Postsecondary | Recreational Therapists | Rehabilitation Counselors | Social and Community Service Managers | Spa Managers | Training and Development Managers | Training and Development Specialists</t>
+          <t>مددکاران سلامت جامعه | تکنسین‌های رژیم غذایی | متخصصان رژیم غذایی و تغذیه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | فیزیولوژیست‌های ورزشی | مربیان ورزشی و مدرسان تناسب اندام گروهی | سرپرستان خط اول کارگران خدمات شخصی | متخصصان آموزش بهداشت | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | مشاوران سلامت روان | کمک‌یاران کاردرمانی | کارکنان تفریحات | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | مدیران اسپا | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Conduct needs assessments or surveys to determine interest in, or satisfaction with, wellness and fitness programs, events, or services. | Conduct or facilitate training sessions or seminars for wellness and fitness staff. | Demonstrate proper operation of fitness equipment, such as resistance machines, cardio machines, free weights, or fitness assessment devices. | Develop fitness or wellness classes, such as yoga, aerobics, strength training, or aquatics, ensuring a diversity of class offerings. | Develop marketing campaigns to promote a healthy lifestyle or participation in fitness or wellness programs. | Develop or coordinate fitness and wellness programs or services. | Evaluate fitness and wellness programs to determine their effectiveness. | Interpret insurance data or Health Reimbursement Account (HRA) data to develop programs that address specific needs of target populations. | Maintain or arrange for maintenance of fitness equipment or facilities. | Maintain wellness- and fitness-related schedules, records, or reports. | Manage or oversee fitness or recreation facilities, ensuring safe and clean facilities and equipment. | Organize and oversee events such as organized runs or walks. | Organize and oversee fitness or wellness programs, such as information presentations, blood drives, or training in first aid or cardiopulmonary resuscitation (CPR). | Organize and oversee health screenings or other preventive measures, such as mammography, blood pressure, or cholesterol screenings or flu vaccinations. | Prepare or implement budgets and strategic, operational, purchasing, or maintenance plans. | Provide individual support or counseling in general wellness or nutrition. | Recommend or approve new program or service offerings to promote wellness and fitness, produce revenues, or minimize costs. | Respond to customer, public, or media requests for information about wellness programs or services. | Select or supervise contractors, such as event hosts or health, fitness, and wellness practitioners. | Supervise fitness or wellness specialists, such as fitness instructors, nutritionists, or health educators. | Teach fitness classes to improve strength, flexibility, cardiovascular conditioning, or general fitness of participants. | Track attendance, participation, or performance data related to wellness events. | Track cost-containment strategies and programs to evaluate effectiveness. | Use computer skills and software to manage Web sites or databases, publish newsletters, or provide webinars.</t>
+          <t>انجام نیازسنجی یا نظرسنجی برای تعیین میزان علاقه به برنامه‌ها، رویدادها یا خدمات سلامتی و تناسب اندام، یا رضایت از آن‌ها. | برگزاری یا تسهیل دوره‌های آموزشی یا سمینارها برای کارکنان حوزه سلامتی و تناسب اندام. | نمایش نحوه صحیح کار با تجهیزات تناسب اندام، مانند دستگاه‌های مقاومتی، دستگاه‌های هوازی، وزنه‌های آزاد یا دستگاه‌های ارزیابی آمادگی جسمانی. | طراحی کلاس‌های تناسب اندام یا سلامتی، مانند یوگا، ایروبیک، تمرینات قدرتی یا ورزش‌های آبی، با اطمینان از تنوع کلاس‌های ارائه‌شده. | تدوین کمپین‌های بازاریابی برای ترویج سبک زندگی سالم یا مشارکت در برنامه‌های تناسب اندام و سلامتی. | تدوین یا هماهنگی برنامه‌ها یا خدمات تناسب اندام و سلامتی. | ارزیابی برنامه‌های تناسب اندام و سلامتی برای تعیین میزان اثربخشی آن‌ها. | تفسیر داده‌های بیمه یا داده‌های حساب بازپرداخت سلامت (HRA) برای تدوین برنامه‌هایی که نیازهای خاص جوامع هدف را برطرف کند. | نگهداری تجهیزات یا تأسیسات ورزشی، یا ترتیب دادن نگهداری آن‌ها. | نگهداری برنامه‌های زمانی، سوابق یا گزارش‌های مرتبط با سلامتی و تناسب اندام. | مدیریت یا نظارت بر تأسیسات ورزشی یا تفریحی، با اطمینان از ایمن و پاکیزه بودن تأسیسات و تجهیزات. | سازماندهی و نظارت بر رویدادهایی مانند دوهای همگانی یا پیاده‌روی‌های سازمان‌یافته. | سازماندهی و نظارت بر برنامه‌های تناسب اندام یا سلامتی، مانند ارائه اطلاعات، اهدای خون یا آموزش کمک‌های اولیه و احیای قلبی‌ریوی (CPR). | سازماندهی و نظارت بر غربالگری‌های سلامت یا سایر اقدامات پیشگیرانه، مانند ماموگرافی، غربالگری فشار خون یا کلسترول، یا واکسیناسیون آنفلوانزا. | تهیه یا اجرای بودجه و برنامه‌های راهبردی، عملیاتی، خرید یا نگهداری. | ارائه پشتیبانی یا مشاوره فردی در زمینه سلامت عمومی یا تغذیه. | پیشنهاد یا تأیید برنامه‌ها و خدمات جدید برای ترویج سلامتی و تناسب اندام، ایجاد درآمد یا کاهش هزینه‌ها. | پاسخ‌گویی به درخواست‌های مشتریان، عموم مردم یا رسانه‌ها برای دریافت اطلاعات درباره برنامه‌ها یا خدمات سلامتی. | انتخاب یا سرپرستی پیمانکاران، مانند مجریان رویدادها یا متخصصان حوزه سلامت، تناسب اندام و سلامتی. | سرپرستی متخصصان تناسب اندام یا سلامتی، مانند مربیان ورزشی، متخصصان تغذیه یا مربیان بهداشت. | تدریس کلاس‌های تناسب اندام برای بهبود قدرت، انعطاف‌پذیری، آمادگی قلبی‌عروقی یا آمادگی جسمانی عمومی شرکت‌کنندگان. | ثبت و پیگیری داده‌های حضور، مشارکت یا عملکرد مرتبط با رویدادهای سلامتی. | پیگیری راهبردها و برنامه‌های مهار هزینه برای ارزیابی اثربخشی آن‌ها. | به‌کارگیری مهارت‌های رایانه‌ای و نرم‌افزارها برای مدیریت وب‌سایت‌ها یا پایگاه‌های داده، انتشار خبرنامه یا برگزاری وبینار.</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spa Managers (مدیران اسپا)</t>
+          <t>مدیران اسپا (Spa Managers)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Massage Department Manager | Salon Manager | Spa Director | Spa Manager | Spa and Guest Experience Director</t>
+          <t>مدیر بخش ماساژ | مدیر سالن | مدیر ارشد اسپا | مدیر اسپا | مدیر ارشد اسپا و تجربه مهمان</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Monitoring | Speaking | Critical Thinking | Active Listening | Active Learning | Reading Comprehension | Learning Strategies | Writing</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Administrative | Customer and Personal Service | Administration and Management | English Language | Education and Training | Personnel and Human Resources | Sales and Marketing | Mathematics | Economics and Accounting</t>
+          <t>اداری | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | آموزش و پرورش | پرسنل و منابع انسانی | فروش و بازاریابی | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Speech Recognition | Speech Clarity | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Fluency of Ideas | Written Expression | Information Ordering | Category Flexibility | Near Vision | Originality | Selective Attention | Number Facility</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | درک کتبی | روانی ایده‌ها | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | اصالت | توجه انتخابی | توانایی عددی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Indoors, Environmentally Controlled | Freedom to Make Decisions | Physical Proximity | E-Mail | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Time Pressure</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Barbers | Concierges | Exercise Trainers and Group Fitness Instructors | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Personal Service Workers | Fitness and Wellness Coordinators | Food Service Managers | Hairdressers, Hairstylists, and Cosmetologists | Hotel, Motel, and Resort Desk Clerks | Locker Room, Coatroom, and Dressing Room Attendants | Lodging Managers | Massage Therapists | Medical Secretaries and Administrative Assistants | Medical and Health Services Managers | Receptionists and Information Clerks | Skincare Specialists | Training and Development Managers</t>
+          <t>آرایشگران مردانه | کانسرج‌ها | مربیان ورزشی و مدرسان تناسب اندام گروهی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول کارگران خدمات شخصی | هماهنگ‌کنندگان تناسب اندام و سلامتی | مدیران خدمات غذایی | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | مدیران اقامتی | ماساژدرمانگران | منشی‌های پزشکی و دستیاران اداری | مدیران خدمات پزشکی و بهداشتی | متصدیان پذیرش و کارمندان اطلاعات | متخصصان مراقبت از پوست | مدیران آموزش و توسعه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Assess employee performance and suggest ways to improve work. | Check spa equipment to ensure proper functioning. | Coordinate facility schedules to maximize usage and efficiency. | Develop or implement marketing strategies. | Develop staff service or retail goals and guide staff in goal achievement. | Direct facility maintenance or repair. | Establish spa budgets and financial goals. | Inform staff of job responsibilities, performance expectations, client service standards, or corporate policies and guidelines. | Inventory products and order new supplies. | Maintain client databases. | Monitor operations to ensure compliance with applicable health, safety, or hygiene standards. | Participate in continuing education classes to maintain current knowledge of industry. | Perform accounting duties, such as recording daily cash flow, preparing bank deposits, or generating financial statements. | Plan or direct spa services and programs. | Recruit, interview, or hire employees. | Respond to customer inquiries or complaints. | Schedule guest appointments. | Schedule staff or supervise scheduling. | Sell products, services, or memberships. | Train staff in the use or sale of products, programs, or activities. | Verify staff credentials, such as educational and certification requirements.</t>
+          <t>ارزیابی عملکرد کارکنان و ارائه پیشنهاد برای بهبود کار. | بررسی تجهیزات اسپا برای اطمینان از عملکرد صحیح آن‌ها. | هماهنگی برنامه‌های زمانی مجموعه برای بیشینه‌سازی بهره‌برداری و کارایی. | تدوین یا اجرای راهبردهای بازاریابی. | تعیین اهداف خدماتی یا فروش برای کارکنان و راهنمایی آنان در تحقق این اهداف. | هدایت امور نگهداری یا تعمیر تأسیسات. | تعیین بودجه و اهداف مالی اسپا. | آگاه‌سازی کارکنان از شرح وظایف، انتظارات عملکردی، استانداردهای خدمات به مشتری، یا سیاست‌ها و دستورالعمل‌های سازمانی. | انبارگردانی محصولات و سفارش اقلام جدید. | نگهداری پایگاه‌های داده مشتریان. | پایش عملیات برای اطمینان از رعایت استانداردهای بهداشتی، ایمنی یا نظافتی مربوطه. | شرکت در دوره‌های آموزش مداوم برای به‌روز نگه‌داشتن دانش صنعت. | انجام امور حسابداری، مانند ثبت گردش نقدی روزانه، تهیه اسناد واریز بانکی یا تنظیم صورت‌های مالی. | برنامه‌ریزی یا هدایت خدمات و برنامه‌های اسپا. | جذب، مصاحبه یا استخدام کارکنان. | پاسخ‌گویی به پرسش‌ها یا شکایت‌های مشتریان. | زمان‌بندی نوبت مراجعان. | زمان‌بندی کارکنان یا نظارت بر برنامه‌ریزی زمانی آنان. | فروش محصولات، خدمات یا عضویت‌ها. | آموزش کارکنان در زمینه استفاده یا فروش محصولات، برنامه‌ها یا فعالیت‌ها. | احراز صلاحیت کارکنان، از جمله الزامات تحصیلی و گواهی‌نامه‌ای.</t>
         </is>
       </c>
     </row>
@@ -607,42 +607,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Managers, All Other (مدیران، سایر موارد)</t>
+          <t>مدیران، سایر موارد (Managers, All Other)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Business Manager | Department Manager | Director of Operations | District Manager | Division Manager | General Manager | Operations Director | Program Manager | Regional Manager | Unit Manager</t>
+          <t>مدیر کسب‌وکار | مدیر بخش | مدیر عملیات | مدیر منطقه | مدیر بخش | مدیر کل | مدیر عملیات | مدیر برنامه | مدیر منطقه‌ای | مدیر واحد</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat | Microsoft Project | نرم‌افزار SAP | سیستم ERP | سیستم HRMS | Microsoft Power BI</t>
+          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat | Microsoft Project | نرم‌افزار SAP | سیستم برنامه‌ریزی منابع سازمانی ERP | سیستم مدیریت منابع انسانی HRMS | Microsoft Power BI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Administration and Management | Personnel and Human Resources | English Language | Customer and Personal Service | Economics and Accounting | Education and Training | Computers and Electronics | Law and Government | Sales and Marketing | Communications and Media</t>
+          <t>مدیریت و اداره | پرسنل و منابع انسانی | زبان انگلیسی | خدمات مشتری و شخصی | اقتصاد و حسابداری | آموزش و پرورش | رایانه و الکترونیک | قانون و دولت | فروش و بازاریابی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Public Speaking | Conflict Situations | Level of Competition</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Chief Executives | General and Operations Managers | Administrative Services Managers | Facilities Managers | Financial Managers | Industrial Production Managers | Purchasing Managers | Transportation, Storage, and Distribution Managers | Human Resources Managers | Training and Development Managers | Compensation and Benefits Managers | Marketing Managers | Sales Managers | Public Relations Managers | Fundraising Managers | Computer and Information Systems Managers | Medical and Health Services Managers | Social and Community Service Managers | Property, Real Estate, and Community Association Managers | Construction Managers</t>
+          <t>مدیران ارشد اجرایی | مدیران عمومی و عملیات | مدیران خدمات اداری | مدیران تسهیلات | مدیران مالی | مدیران تولید صنعتی | مدیران خرید | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران منابع انسانی | مدیران آموزش و توسعه | مدیران جبران خدمات و مزایا | مدیران بازاریابی | مدیران فروش | مدیران روابط عمومی | مدیران جمع‌آوری کمک‌های مالی | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران خدمات پزشکی و بهداشتی | مدیران خدمات اجتماعی و جامعه | مدیران املاک، مستغلات و انجمن‌های اجتماعی | مدیران ساخت‌وساز</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Plan, direct, and coordinate the operations of organizations or departments not classified separately. | Establish departmental goals, objectives, policies, and operating procedures. | Direct and coordinate the activities of supervisory and professional staff. | Prepare, justify, and administer operating and capital budgets. | Analyze operating and financial data to evaluate performance against objectives. | Recruit, hire, train, and evaluate personnel and recommend personnel actions. | Negotiate and approve contracts, agreements, and purchases of goods and services. | Ensure compliance with applicable laws, regulations, and organizational policies. | Prepare reports and presentations for senior management and governing bodies. | Identify process improvements and implement changes to increase efficiency. | Resolve escalated operational problems, customer issues, and staff disputes. | Represent the organization in dealings with clients, vendors, and outside agencies. | Monitor industry trends and competitor activity to inform planning decisions. | Direct the allocation of staff, equipment, and facilities across projects.</t>
+          <t>برنامه‌ریزی، هدایت و هماهنگی عملیات سازمان‌ها یا واحدهایی که جداگانه طبقه‌بندی نشده‌اند. | تعیین اهداف کلان، اهداف عملیاتی، سیاست‌ها و رویه‌های اجرایی واحد سازمانی. | هدایت و هماهنگی فعالیت‌های کارکنان سرپرست و متخصص. | تهیه، توجیه و اداره بودجه‌های جاری و سرمایه‌ای. | تجزیه و تحلیل داده‌های عملیاتی و مالی برای ارزیابی عملکرد در برابر اهداف. | جذب، استخدام، آموزش و ارزیابی کارکنان و ارائه پیشنهاد درباره اقدامات پرسنلی. | مذاکره و تأیید قراردادها، توافق‌نامه‌ها و خرید کالاها و خدمات. | حصول اطمینان از رعایت قوانین، مقررات و سیاست‌های سازمانی مربوطه. | تهیه گزارش‌ها و ارائه‌ها برای مدیریت ارشد و هیئت‌های حاکمیتی. | شناسایی فرصت‌های بهبود فرایند و اجرای تغییرات برای افزایش کارایی. | رفع مشکلات عملیاتی ارجاع‌شده، مسائل مشتریان و اختلافات کارکنان. | نمایندگی سازمان در تعامل با مشتریان، تأمین‌کنندگان و نهادهای بیرونی. | پایش روندهای صنعت و فعالیت رقبا برای پشتیبانی از تصمیم‌های برنامه‌ریزی. | هدایت تخصیص کارکنان، تجهیزات و امکانات میان پروژه‌ها.</t>
         </is>
       </c>
     </row>
@@ -664,42 +664,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Managers (مدیران امور نظارتی)</t>
+          <t>مدیران امور نظارتی (Regulatory Affairs Managers)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CMC Director (Chemistry, Manufacturing, and Controls Director) | Compliance Director | Global RA Director (Global Regulatory Affairs Director) | Global RA Manager (Global Regulatory Affairs Manager) | RA Director (Regulatory Affairs Director) | RA Manager (Regulatory Affairs Manager) | RA QA Director (Regulatory Affairs Quality Assurance Director) | RA VP (Regulatory Affairs Vice President) | Regulatory Director | Vaccine RA Director (Vaccine Regulatory Affairs Director)</t>
+          <t>مدیر CMC (شیمی، تولید و کنترل) | مدیر ارشد انطباق | مدیر ارشد امور نظارتی جهانی (Global RA) | مدیر امور نظارتی جهانی (Global RA) | مدیر ارشد امور نظارتی (RA) | مدیر امور نظارتی (RA) | مدیر ارشد امور نظارتی و تضمین کیفیت (RA QA) | معاون امور نظارتی (RA VP) | مدیر ارشد امور نظارتی | مدیر ارشد امور نظارتی واکسن (Vaccine RA)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adlib Express | Adobe Acrobat | Analyse-it | Aris Global Register | Axway eSubmissions | نرم‌افزار پایگاه داده | Datafarm S-Cubed | Datafarm a-Pulse | Datafarm eCTDGatekeeper | Datafarm eCTDViewer | Dialog DialogLink | نرم‌افزار انتشار اسناد | DoubleBridge ROSETTA Phoenix eCTD Viewer | DoubleBridge ROSETTA Pyramid | DoubleBridge ROSETTA Sceptre | DoubleBridge ROSETTA Scribe | نرم‌افزار eCTD | نرم‌افزار اعتبارسنجی eCTD | نرم‌افزار مشاهده eCTD | سیستم EDMS | نرم‌افزار ECM | Extedo DOCvalidator | Extedo PLmanager | Extedo eCTDmanager Suite | GlobalSubmit REVIEW | GlobalSubmit VALIDATE | IBM Notes | Image Solutions ISIPublisher | Image Solutions eCTDXpress | نرم‌افزار IDE | Lorenz DocuBridge | Lorenz eValidator | Lorenz labelBridge | MasterControl software | MedXView eCTDauditor | MediRegs E-dition Compliance Monitor | MediRegs Pharmaceutical Regulation Suite | MediRegs Regulation and Reimbursement Suite | MediRegs Risk Assessment Manager | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Octagon StartingPoint | Octagon ViewPoint eCTD Complete | Pilgrim Regulatory Submission | نرم‌افزار مدیریت ریسک | SAP EHS Management | نرم‌افزار SAP | Samarind RMS | ابزارهای توسعه نرم‌افزار | نرم‌افزار تحلیل آماری | SQL | Tableau | Take Solutions PharmaReady Document Management System | Thomson Reuters Liquent CoreDossier Submission Accelerator for eCTD | Thomson Reuters Liquent InSight Suite | نرم‌افزار TQM | Virtify eCTD | نرم‌افزار مرورگر وب | نرم‌افزار نویسندگی XML</t>
+          <t>Adlib Express | Adobe Acrobat | Analyse-it | Aris Global Register | Axway eSubmissions | نرم‌افزار پایگاه داده | Datafarm S-Cubed | Datafarm a-Pulse | Datafarm eCTDGatekeeper | Datafarm eCTDViewer | Dialog DialogLink | نرم‌افزار انتشار اسناد | DoubleBridge ROSETTA Phoenix eCTD Viewer | DoubleBridge ROSETTA Pyramid | DoubleBridge ROSETTA Sceptre | DoubleBridge ROSETTA Scribe | نرم‌افزار eCTD | نرم‌افزار اعتبارسنجی eCTD | نرم‌افزار مشاهده eCTD | سیستم EDMS | نرم‌افزار ECM | Extedo DOCvalidator | Extedo PLmanager | Extedo eCTDmanager Suite | GlobalSubmit REVIEW | GlobalSubmit VALIDATE | IBM Notes | Image Solutions ISIPublisher | Image Solutions eCTDXpress | نرم‌افزار محیط توسعه یکپارچه IDE | Lorenz DocuBridge | Lorenz eValidator | Lorenz labelBridge | نرم‌افزار MasterControl | MedXView eCTDauditor | MediRegs E-dition Compliance Monitor | MediRegs Pharmaceutical Regulation Suite | MediRegs Regulation and Reimbursement Suite | MediRegs Risk Assessment Manager | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Octagon StartingPoint | Octagon ViewPoint eCTD Complete | Pilgrim Regulatory Submission | نرم‌افزار مدیریت ریسک | SAP EHS Management | نرم‌افزار SAP | Samarind RMS | ابزارهای توسعه نرم‌افزار | نرم‌افزار تحلیل آماری | زبان پرس‌وجوی ساختاریافته SQL | Tableau | Take Solutions PharmaReady Document Management System | Thomson Reuters Liquent CoreDossier Submission Accelerator for eCTD | Thomson Reuters Liquent InSight Suite | نرم‌افزار TQM | Virtify eCTD | نرم‌افزار مرورگر وب | نرم‌افزار نویسندگی XML</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Writing | Reading Comprehension | Speaking | Active Listening | Critical Thinking | Monitoring | Active Learning | Learning Strategies</t>
+          <t>نگارش | درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>English Language | Law and Government | Administration and Management | Biology | Education and Training | Administrative | Chemistry</t>
+          <t>زبان انگلیسی | قانون و دولت | مدیریت و اداره | زیست‌شناسی | آموزش و پرورش | اداری | شیمی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Written Expression | Written Comprehension | Oral Expression | Oral Comprehension | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Near Vision | Speech Recognition | Speech Clarity | Information Ordering | Fluency of Ideas | Originality | Category Flexibility</t>
+          <t>بیان کتبی | درک کتبی | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>E-Mail | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Contact With Others | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Time Pressure | Frequency of Decision Making</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فشار زمانی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Administrative Services Managers | Chief Executives | Chief Sustainability Officers | Clinical Data Managers | Compliance Managers | Compliance Officers | Environmental Compliance Inspectors | Environmental Scientists and Specialists, Including Health | Financial Examiners | Financial Risk Specialists | Government Property Inspectors and Investigators | Health Information Technologists and Medical Registrars | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Management Analysts | Medical and Health Services Managers | Natural Sciences Managers | Project Management Specialists | Public Relations Managers | Quality Control Systems Managers | Regulatory Affairs Specialists</t>
+          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | مدیران ارشد پایداری | مدیران داده‌های بالینی | مدیران انطباق | افسران انطباق | بازرسان انطباق زیست‌محیطی | دانشمندان و متخصصان محیط زیست، شامل بهداشت | بازرسان مالی | متخصصان ریسک مالی | بازرسان و محققان اموال دولتی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | مدیران علوم طبیعی | متخصصان مدیریت پروژه | مدیران روابط عمومی | مدیران سیستم‌های کنترل کیفیت | متخصصان امور نظارتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Communicate regulatory information to multiple departments and ensure that information is interpreted correctly. | Contribute to the development or implementation of business unit strategic and operating plans. | Coordinate internal discoveries and depositions with legal department staff. | Develop and maintain standard operating procedures or local working practices. | Develop regulatory strategies and implementation plans for the preparation and submission of new products. | Develop relationships with state or federal environmental regulatory agencies to learn about and analyze the potential impacts of proposed environmental policy regulations. | Direct documentation efforts to ensure compliance with domestic and international regulations and standards. | Direct the preparation and submission of regulatory agency applications, reports, or correspondence. | Establish procedures or systems for publishing document submissions in hardcopy or electronic formats. | Establish regulatory priorities or budgets and allocate resources and workloads. | Evaluate new software publishing systems and confer with regulatory agencies concerning news or updates on electronic publishing of submissions. | Evaluate regulatory affairs aspects that are specifically green, such as the use of toxic substances in packaging, carbon footprinting issues, or green policy implementation. | Formulate or implement regulatory affairs policies and procedures to ensure that regulatory compliance is maintained or enhanced. | Implement or monitor complaint processing systems to ensure effective and timely resolution of all complaint investigations. | Investigate product complaints and prepare documentation and submissions to appropriate regulatory agencies as necessary. | Maintain current knowledge of relevant regulations, including proposed and final rules. | Manage activities such as audits, regulatory agency inspections, or product recalls. | Monitor emerging trends regarding industry regulations to determine potential impacts on organizational processes. | Monitor regulatory affairs activities to ensure their alignment with corporate sustainability or green initiatives. | Monitor regulatory affairs trends related to environmental issues. | Participate in the development or implementation of clinical trial protocols. | Provide regulatory guidance to departments or development project teams regarding design, development, evaluation, or marketing of products. | Provide responses to regulatory agencies regarding product information or issues. | Represent organizations before domestic or international regulatory agencies on major policy matters or decisions regarding company products. | Review all regulatory agency submission materials to ensure timeliness, accuracy, comprehensiveness, or compliance with regulatory standards. | Review materials such as marketing literature or user manuals to ensure that regulatory agency requirements are met. | Train staff in regulatory policies or procedures.</t>
+          <t>انتقال اطلاعات نظارتی به واحدهای مختلف و حصول اطمینان از تفسیر صحیح این اطلاعات. | مشارکت در تدوین یا اجرای برنامه‌های راهبردی و عملیاتی واحد کسب‌وکار. | هماهنگی فرایندهای کشف اسناد و اخذ اظهارات داخلی با کارکنان واحد حقوقی. | تدوین و نگهداری رویه‌های اجرایی استاندارد یا شیوه‌های کاری محلی. | تدوین راهبردهای نظارتی و برنامه‌های اجرایی برای تهیه و ارائه پرونده محصولات جدید. | برقراری ارتباط با نهادهای نظارتی محیط‌زیستی ایالتی یا فدرال برای آگاهی از پیامدهای احتمالی مقررات پیشنهادی محیط‌زیستی و تحلیل آن‌ها. | هدایت امور مستندسازی برای حصول اطمینان از رعایت مقررات و استانداردهای داخلی و بین‌المللی. | هدایت تهیه و ارائه درخواست‌ها، گزارش‌ها یا مکاتبات مربوط به نهادهای نظارتی. | استقرار رویه‌ها یا سامانه‌هایی برای انتشار اسناد ارسالی به‌صورت چاپی یا الکترونیکی. | تعیین اولویت‌ها یا بودجه امور نظارتی و تخصیص منابع و حجم کار. | ارزیابی سامانه‌های جدید انتشار نرم‌افزاری و رایزنی با نهادهای نظارتی درباره اخبار یا به‌روزرسانی‌های انتشار الکترونیکی اسناد. | ارزیابی جنبه‌های سبز امور نظارتی، مانند استفاده از مواد سمی در بسته‌بندی، مسائل ردپای کربن، یا اجرای سیاست‌های سبز. | تدوین یا اجرای سیاست‌ها و رویه‌های امور نظارتی برای حفظ یا ارتقای انطباق با مقررات. | اجرا یا پایش سامانه‌های رسیدگی به شکایات برای حصول اطمینان از رسیدگی مؤثر و به‌موقع به همه شکایات. | بررسی شکایت‌های مربوط به محصول و تهیه مستندات و پرونده‌های لازم برای ارائه به نهادهای نظارتی ذی‌ربط. | به‌روز نگه‌داشتن دانش مقررات مربوطه، از جمله مقررات پیشنهادی و نهایی. | مدیریت فعالیت‌هایی مانند ممیزی، بازرسی نهادهای نظارتی یا فراخوان جمع‌آوری محصول. | پایش روندهای نوظهور مقررات صنعت برای تعیین پیامدهای احتمالی آن بر فرایندهای سازمان. | پایش فعالیت‌های امور نظارتی برای اطمینان از همسویی آن‌ها با ابتکارهای پایداری یا سبز شرکت. | پایش روندهای امور نظارتی مرتبط با مسائل محیط‌زیستی. | مشارکت در تدوین یا اجرای پروتکل‌های کارآزمایی بالینی. | ارائه راهنمایی نظارتی به واحدها یا تیم‌های پروژه توسعه در زمینه طراحی، توسعه، ارزیابی یا بازاریابی محصولات. | ارائه پاسخ به نهادهای نظارتی درباره اطلاعات یا مسائل محصول. | نمایندگی سازمان نزد نهادهای نظارتی داخلی یا بین‌المللی در موضوعات یا تصمیم‌های مهم سیاستی مرتبط با محصولات شرکت. | بازبینی همه مدارک ارسالی به نهادهای نظارتی برای اطمینان از به‌موقع بودن، دقت، جامعیت یا انطباق با استانداردهای نظارتی. | بازبینی مدارکی مانند ادبیات بازاریابی یا راهنمای کاربر برای اطمینان از رعایت الزامات نهادهای نظارتی. | آموزش کارکنان در زمینه سیاست‌ها یا رویه‌های نظارتی.</t>
         </is>
       </c>
     </row>
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Compliance Managers (مدیران انطباق)</t>
+          <t>مدیران انطباق (Compliance Managers)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Accreditation Lieutenant | Accreditation Manager | Compliance Director | Compliance Manager | Compliance Operations Manager | Environmental Health and Safety Director | Environmental Manager | Environmental Program Manager | Health, Safety, and Environmental Manager (HSE Manager) | Risk Manager</t>
+          <t>افسر اعتباربخشی | مدیر اعتباربخشی | مدیر ارشد انطباق | مدیر انطباق | مدیر عملیات انطباق | مدیر ارشد بهداشت، ایمنی و محیط‌زیست | مدیر محیط‌زیست | مدیر برنامه زیست‌محیطی | مدیر بهداشت، ایمنی و محیط‌زیست (HSE) | مدیر ریسک</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>80-20 Software Leaders4 | ARC Logics Sword | Actimize Brokerage Compliance Solutions | Adobe Acrobat | Agiliance Compliance Manager | Aline GRC | Apple Safari | Archer Compliance Management | AssurX CATSWeb | AssurX Financial Services Compliance Management System | Audit2 AdaptiveGRC | Axentis Compliance Management | BPS Compliance | BWise Compliance Management | CMO Compliance Regulatory Compliance Solution | Compliance 360 | Compliance11 Supervisory Suite | ComplianceBridge Total Compliance | ControlCase Compliance Manager | Cura Software Solutions Cura for Compliance Management | نرم‌افزار تحلیل داده | نرم‌افزار مدیریت پایگاه داده | DoubleCheck GRC&amp;T Platform | نرم‌افزار ایمیل | EtQ Environmental Health and Safety Software | EtQ FDA cGxP Compliance Software for Life Sciences | FRSGlobal RegPro | Fidessa Compliance Manager | نرم‌افزار GRC | Guideline Risk Technologies RUBI | HCPCS | Horwath Software Magique | سیستم HRIS | IBM Notes | Keane SCORE | LRN Ethics and Compliance Alliance | LexisNexis | MasterControl MD | MasterControl TotalPharma | MediRegs ComplyTrack | Methodware ERA | MetricStream Compliance Management | MetricStream Enterprise Compliance Platform | MetricStream Regulatory Reporting | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Modulo Risk Manager | Mozilla Firefox | MyComplianceOffice Compliance Operations Management System | Neohapsis Certus GRC | Oracle Enterprise Governance, Risk, and Compliance Manager | Oracle Insurance Compliance Tracker | Protiviti Governance Portal | QUMAS quality management solution software | RVR Systems Compliance | Resolve Legislative Compliance Management | SAP BEx Report Designer | نرم‌افزار زمان‌بندی | StataCorp Stata | Sword Achiever Compliance Portal Dashboard | نرم‌افزار حسابداری مالیاتی | نرم‌افزار مالیاتی | The Garland Group RiskKey | Thomson Reuters Paisley Enterprise GRC | نرم‌افزار مرورگر وب | policyIQ</t>
+          <t>80-20 Software Leaders4 | ARC Logics Sword | Actimize Brokerage Compliance Solutions | Adobe Acrobat | Agiliance Compliance Manager | Aline GRC | Apple Safari | Archer Compliance Management | AssurX CATSWeb | AssurX Financial Services Compliance Management System | Audit2 AdaptiveGRC | Axentis Compliance Management | BPS Compliance | BWise Compliance Management | CMO Compliance Regulatory Compliance Solution | Compliance 360 | Compliance11 Supervisory Suite | ComplianceBridge Total Compliance | ControlCase Compliance Manager | Cura Software Solutions Cura for Compliance Management | نرم‌افزار تحلیل داده | نرم‌افزار مدیریت پایگاه داده | DoubleCheck GRC&amp;T Platform | نرم‌افزار ایمیل | EtQ Environmental Health and Safety Software | EtQ FDA cGxP Compliance Software for Life Sciences | FRSGlobal RegPro | Fidessa Compliance Manager | نرم‌افزار GRC | Guideline Risk Technologies RUBI | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Horwath Software Magique | سیستم اطلاعات منابع انسانی (HRIS) | IBM Notes | Keane SCORE | LRN Ethics and Compliance Alliance | LexisNexis | MasterControl MD | MasterControl TotalPharma | MediRegs ComplyTrack | Methodware ERA | MetricStream Compliance Management | MetricStream Enterprise Compliance Platform | MetricStream Regulatory Reporting | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Modulo Risk Manager | Mozilla Firefox | MyComplianceOffice Compliance Operations Management System | Neohapsis Certus GRC | Oracle Enterprise Governance, Risk, and Compliance Manager | Oracle Insurance Compliance Tracker | Protiviti Governance Portal | نرم‌افزار راهکار مدیریت کیفیت QUMAS | RVR Systems Compliance | Resolve Legislative Compliance Management | SAP BEx Report Designer | نرم‌افزار زمان‌بندی | StataCorp Stata | Sword Achiever Compliance Portal Dashboard | نرم‌افزار حسابداری مالیاتی | نرم‌افزار مالیاتی | The Garland Group RiskKey | Thomson Reuters Paisley Enterprise GRC | نرم‌افزار مرورگر وب | policyIQ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Critical Thinking | Active Listening | Writing | Speaking | Active Learning | Monitoring | Learning Strategies</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Law and Government | English Language | Administration and Management | Customer and Personal Service | Personnel and Human Resources | Computers and Electronics | Education and Training | Administrative | Public Safety and Security</t>
+          <t>قانون و دولت | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | رایانه و الکترونیک | آموزش و پرورش | اداری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Written Expression | Problem Sensitivity | Oral Expression | Oral Comprehension | Written Comprehension | Deductive Reasoning | Inductive Reasoning | Speech Clarity | Near Vision | Speech Recognition | Information Ordering | Category Flexibility | Selective Attention | Fluency of Ideas | Far Vision</t>
+          <t>بیان کتبی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Contact With Others | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Time Pressure | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Health and Safety of Other Workers | Spend Time Sitting | Deal With External Customers or the Public in General | Work Outcomes and Results of Other Workers | Importance of Repeating Same Tasks | Written Letters and Memos</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Administrative Services Managers | Chief Executives | Compensation, Benefits, and Job Analysis Specialists | Compliance Officers | Document Management Specialists | Environmental Compliance Inspectors | Financial Examiners | Financial Risk Specialists | Fraud Examiners, Investigators and Analysts | Government Property Inspectors and Investigators | Health Information Technologists and Medical Registrars | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Information Security Analysts | Information Security Engineers | Management Analysts | Regulatory Affairs Managers | Regulatory Affairs Specialists | Retail Loss Prevention Specialists | Security Management Specialists | Security Managers</t>
+          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | متخصصان جبران خدمات، مزایا و تحلیل شغل | افسران انطباق | متخصصان مدیریت اسناد | بازرسان انطباق زیست‌محیطی | بازرسان مالی | متخصصان ریسک مالی | بازرسان، محققان و تحلیلگران کلاهبرداری | بازرسان و محققان اموال دولتی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت | مدیران امور نظارتی | متخصصان امور نظارتی | متخصصان پیشگیری از خسارت خرده‌فروشی | متخصصان مدیریت امنیت | مدیران امنیتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Advise internal management or business partners on the implementation or operation of compliance programs. | Advise technical professionals on the development or use of environmental compliance or reporting tools. | Collaborate with human resources departments to ensure the implementation of consistent disciplinary action strategies in cases of compliance standard violations. | Conduct environmental audits to ensure adherence to environmental standards. | Conduct or direct the internal investigation of compliance issues. | Conduct periodic internal reviews or audits to ensure that compliance procedures are followed. | Consult with corporate attorneys as necessary to address difficult legal compliance issues. | Design or implement improvements in communication, monitoring, or enforcement of compliance standards. | Develop risk management strategies based on assessment of product, compliance, or operational risks. | Direct environmental programs, such as air or water compliance, aboveground or underground storage tanks, spill prevention or control, hazardous waste or materials management, solid waste recycling, medical waste management, indoor air quality, integrated pest management, employee training, or disaster preparedness. | Direct the development or implementation of policies and procedures related to compliance throughout an organization. | Discuss emerging compliance issues to ensure that management and employees are informed about compliance reporting systems, policies, and practices. | Disseminate written policies and procedures related to compliance activities. | Evaluate testing procedures to meet the specifications of environmental monitoring programs. | File appropriate compliance reports with regulatory agencies. | Identify compliance issues that require follow-up or investigation. | Keep informed regarding pending industry changes, trends, or best practices. | Maintain documentation of compliance activities, such as complaints received or investigation outcomes. | Monitor compliance systems to ensure their effectiveness. | Oversee internal reporting systems, such as corporate compliance hotlines. | Prepare management reports regarding compliance operations and progress. | Provide assistance to internal or external auditors in compliance reviews. | Provide employee training on compliance related topics, policies, or procedures. | Report violations of compliance or regulatory standards to duly authorized enforcement agencies as appropriate or required. | Review communications such as securities sales advertising to ensure there are no violations of standards or regulations. | Review or modify policies or operating guidelines to comply with changes to environmental standards or regulations. | Serve as a confidential point of contact for employees to communicate with management, seek clarification on issues or dilemmas, or report irregularities. | Verify that all regulatory policies and procedures have been documented, implemented, and communicated. | Verify that software technology is in place to adequately provide oversight and monitoring in all required areas.</t>
+          <t>ارائه مشاوره به مدیریت داخلی یا شرکای تجاری درباره اجرا یا اداره برنامه‌های انطباق. | ارائه مشاوره به متخصصان فنی درباره تدوین یا استفاده از ابزارهای انطباق یا گزارش‌دهی محیط‌زیستی. | همکاری با واحدهای منابع انسانی برای حصول اطمینان از اجرای یکسان راهبردهای اقدام انضباطی در موارد نقض استانداردهای انطباق. | انجام ممیزی‌های محیط‌زیستی برای اطمینان از رعایت استانداردهای محیط‌زیستی. | انجام یا هدایت تحقیقات داخلی درباره مسائل انطباق. | انجام بازبینی‌ها یا ممیزی‌های داخلی دوره‌ای برای اطمینان از رعایت رویه‌های انطباق. | رایزنی با وکلای شرکت در صورت لزوم برای رسیدگی به مسائل دشوار انطباق حقوقی. | طراحی یا اجرای بهبودها در اطلاع‌رسانی، پایش یا اعمال استانداردهای انطباق. | تدوین راهبردهای مدیریت ریسک بر پایه ارزیابی ریسک‌های محصول، انطباق یا عملیات. | هدایت برنامه‌های محیط‌زیستی، مانند انطباق هوا یا آب، مخازن ذخیره روزمینی یا زیرزمینی، پیشگیری یا مهار نشت، مدیریت پسماند یا مواد خطرناک، بازیافت پسماند جامد، مدیریت پسماند پزشکی، کیفیت هوای داخلی، مدیریت تلفیقی آفات، آموزش کارکنان، یا آمادگی در برابر بلایا. | هدایت تدوین یا اجرای سیاست‌ها و رویه‌های مرتبط با انطباق در سراسر سازمان. | بحث درباره مسائل نوظهور انطباق برای حصول اطمینان از آگاهی مدیریت و کارکنان از سامانه‌ها، سیاست‌ها و شیوه‌های گزارش‌دهی انطباق. | انتشار سیاست‌ها و رویه‌های مکتوب مرتبط با فعالیت‌های انطباق. | ارزیابی رویه‌های آزمون برای برآورده کردن مشخصات برنامه‌های پایش محیط‌زیستی. | ارائه گزارش‌های انطباق مقتضی به نهادهای نظارتی. | شناسایی مسائل انطباق که نیازمند پیگیری یا بررسی هستند. | آگاه ماندن از تغییرات، روندها یا بهترین شیوه‌های در پیش روی صنعت. | نگهداری مستندات فعالیت‌های انطباق، مانند شکایت‌های دریافت‌شده یا نتایج بررسی‌ها. | پایش سامانه‌های انطباق برای اطمینان از اثربخشی آن‌ها. | نظارت بر سامانه‌های گزارش‌دهی داخلی، مانند خطوط تلفن گزارش تخلف شرکت. | تهیه گزارش‌های مدیریتی درباره عملیات و پیشرفت امور انطباق. | ارائه کمک به ممیزان داخلی یا خارجی در بازبینی‌های انطباق. | ارائه آموزش به کارکنان در موضوعات، سیاست‌ها یا رویه‌های مرتبط با انطباق. | گزارش موارد نقض استانداردهای انطباق یا مقررات به نهادهای اجرایی دارای صلاحیت، در صورت لزوم یا الزام. | بازبینی اطلاع‌رسانی‌هایی مانند تبلیغات فروش اوراق بهادار برای اطمینان از نبود نقض استانداردها یا مقررات. | بازبینی یا اصلاح سیاست‌ها یا دستورالعمل‌های اجرایی برای انطباق با تغییرات استانداردها یا مقررات محیط‌زیستی. | ایفای نقش به‌عنوان مرجع تماس محرمانه برای کارکنان جهت ارتباط با مدیریت، شفاف‌سازی مسائل یا دوراهی‌ها، یا گزارش تخلفات. | احراز اینکه همه سیاست‌ها و رویه‌های نظارتی مستند، اجرا و اطلاع‌رسانی شده‌اند. | احراز اینکه فناوری نرم‌افزاری لازم برای نظارت و پایش کافی در همه حوزه‌های الزامی مستقر است.</t>
         </is>
       </c>
     </row>
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Loss Prevention Managers (مدیران پیشگیری از زیان)</t>
+          <t>مدیران پیشگیری از زیان (Loss Prevention Managers)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Asset Protection Manager | Logistics Loss Prevention Manager | Loss Control Manager | Loss Prevention Director | Loss Prevention Manager | Loss Prevention Operations Director | Loss Prevention Operations Manager | Loss Prevention Supervisor | Market Asset Protection Manager</t>
+          <t>مدیر حفاظت از دارایی‌ها | مدیر پیشگیری از زیان لجستیک | مدیر کنترل زیان | مدیر ارشد پیشگیری از زیان | مدیر پیشگیری از زیان | مدیر ارشد عملیات پیشگیری از زیان | مدیر عملیات پیشگیری از زیان | سرپرست پیشگیری از خسارت | مدیر حفاظت از دارایی‌های بازار</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Enabl-u Technologies APIS | نرم‌افزار یکپارچه‌سازی برنامه‌های سازمانی (EAI) | نرم‌افزار حسابداری مالی | نرم‌افزار Google Workspace | IBM Lotus Notes | نرم‌افزار ردیابی موجودی | MICROS XBR Loss Prevention | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Windows | Microsoft Word | MySQL | نرم‌افزار مدیریت پرسنل | نرم‌افزار گزارش‌دهی | نرم‌افزار SAP | SQL | نرم‌افزار گزارش‌دهی زمان | نرم‌افزار زمان‌بندی کار</t>
+          <t>Enabl-u Technologies APIS | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | نرم‌افزار حسابداری مالی | نرم‌افزار Google Workspace | IBM Lotus Notes | نرم‌افزار ردیابی موجودی | MICROS XBR Loss Prevention | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Windows | Microsoft Word | MySQL | نرم‌افزار مدیریت پرسنل | نرم‌افزار گزارش‌دهی | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار گزارش‌دهی زمان | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Monitoring | Writing | Active Learning | Learning Strategies</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Public Safety and Security | Law and Government | Administration and Management | English Language | Education and Training | Customer and Personal Service | Psychology | Computers and Electronics | Personnel and Human Resources | Mathematics | Administrative</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | مدیریت و اداره | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | پرسنل و منابع انسانی | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Problem Sensitivity | Oral Expression | Oral Comprehension | Near Vision | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Speech Clarity | Speech Recognition | Originality | Category Flexibility | Selective Attention | Far Vision | Information Ordering | Fluency of Ideas | Flexibility of Closure</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E-Mail | Contact With Others | Telephone Conversations | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Deal With External Customers or the Public in General | Conflict Situations | Time Pressure | Importance of Being Exact or Accurate | Coordinate or Lead Others in Accomplishing Work Activities | Written Letters and Memos | Work Outcomes and Results of Other Workers</t>
+          <t>ایمیل | ارتباط با دیگران | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | فشار زمانی | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Business Continuity Planners | Compensation, Benefits, and Job Analysis Specialists | Compliance Managers | Emergency Management Directors | Environmental Compliance Inspectors | Financial Risk Specialists | First-Line Supervisors of Security Workers | Fraud Examiners, Investigators and Analysts | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Information Security Analysts | Information Security Engineers | Management Analysts | Medical and Health Services Managers | Occupational Health and Safety Specialists | Occupational Health and Safety Technicians | Private Detectives and Investigators | Retail Loss Prevention Specialists | Security Management Specialists | Security Managers | Social and Community Service Managers</t>
+          <t>برنامه‌ریزان تداوم کسب‌وکار | متخصصان جبران خدمات، مزایا و تحلیل شغل | مدیران انطباق | مدیران مدیریت بحران | بازرسان انطباق زیست‌محیطی | متخصصان ریسک مالی | سرپرستان خط اول کارکنان امنیتی | بازرسان، محققان و تحلیلگران کلاهبرداری | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | کارآگاهان و بازرسان خصوصی | متخصصان پیشگیری از خسارت خرده‌فروشی | متخصصان مدیریت امنیت | مدیران امنیتی | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Administer systems and programs to reduce loss, maintain inventory control, or increase safety. | Advise retail establishments on development of loss-investigation procedures. | Advise retail managers on compliance with applicable codes, laws, regulations, or standards. | Analyze retail data to identify current or emerging trends in theft or fraud. | Assess security needs across locations to ensure proper deployment of loss prevention resources, such as staff and technology. | Collaborate with law enforcement to investigate and solve external theft or fraud cases. | Coordinate or conduct internal investigations of problems such as employee theft and violations of corporate loss prevention policies. | Coordinate theft and fraud investigations involving career criminals or organized group activities. | Develop and maintain partnerships with federal, state, or local law enforcement agencies or members of the retail loss prevention community. | Direct installation of covert surveillance equipment, such as security cameras. | Direct loss prevention audit programs including target store audits, maintenance audits, safety audits, or electronic article surveillance (EAS) audits. | Hire or supervise loss prevention staff. | Identify potential for loss and develop strategies to eliminate it. | Investigate or interview individuals suspected of shoplifting or internal theft. | Maintain databases such as bad check logs, reports on multiple offenders, and alarm activation lists. | Maintain documentation of all loss prevention activity. | Monitor and review paperwork procedures and systems to prevent error-related shortages. | Monitor compliance to operational, safety, or inventory control procedures, including physical security standards. | Perform cash audits and deposit investigations to fully account for store cash. | Perform or direct inventory investigations in response to shrink results outside of acceptable ranges. | Provide recommendations and solutions in crisis situations such as workplace violence, protests, and demonstrations. | Recommend improvements in loss prevention programs, staffing, scheduling, or training. | Review loss prevention exception reports and cash discrepancies to ensure adherence to guidelines. | Supervise surveillance, detection, or criminal processing related to theft and criminal cases. | Train loss prevention staff, retail managers, or store employees on loss control and prevention measures. | Verify correct use and maintenance of physical security systems, such as closed-circuit television, merchandise tags, and burglar alarms. | Visit stores to ensure compliance with company policies and procedures.</t>
+          <t>اداره سامانه‌ها و برنامه‌های کاهش زیان، کنترل موجودی یا افزایش ایمنی. | ارائه مشاوره به واحدهای خرده‌فروشی درباره تدوین رویه‌های بررسی زیان. | ارائه مشاوره به مدیران خرده‌فروشی درباره رعایت آیین‌نامه‌ها، قوانین، مقررات یا استانداردهای مربوطه. | تجزیه و تحلیل داده‌های خرده‌فروشی برای شناسایی روندهای جاری یا نوظهور سرقت و تقلب. | ارزیابی نیازهای امنیتی در همه شعب برای اطمینان از استقرار درست منابع پیشگیری از زیان، مانند نیروی انسانی و فناوری. | همکاری با نیروهای انتظامی برای بررسی و حل پرونده‌های سرقت یا تقلب بیرونی. | هماهنگی یا انجام تحقیقات داخلی درباره مشکلاتی مانند سرقت کارکنان و نقض سیاست‌های پیشگیری از زیان شرکت. | هماهنگی تحقیقات سرقت و تقلب مرتبط با مجرمان حرفه‌ای یا فعالیت‌های گروهی سازمان‌یافته. | ایجاد و حفظ همکاری با نهادهای انتظامی فدرال، ایالتی یا محلی یا اعضای جامعه پیشگیری از زیان در خرده‌فروشی. | هدایت نصب تجهیزات نظارت پنهان، مانند دوربین‌های امنیتی. | هدایت برنامه‌های ممیزی پیشگیری از زیان، شامل ممیزی فروشگاه‌های هدف، ممیزی نگهداری، ممیزی ایمنی یا ممیزی سامانه‌های الکترونیکی نظارت بر کالا (EAS). | استخدام یا سرپرستی کارکنان پیشگیری از زیان. | شناسایی احتمال بروز زیان و تدوین راهبردهایی برای حذف آن. | بررسی یا مصاحبه با افراد مظنون به سرقت از فروشگاه یا سرقت داخلی. | نگهداری پایگاه‌های داده مانند سوابق چک‌های برگشتی، گزارش‌های متخلفان مکرر و فهرست فعال‌سازی آژیرها. | نگهداری مستندات همه فعالیت‌های پیشگیری از زیان. | پایش و بازبینی رویه‌ها و سامانه‌های اسناد اداری برای پیشگیری از کسری‌های ناشی از خطا. | پایش رعایت رویه‌های عملیاتی، ایمنی یا کنترل موجودی، از جمله استانداردهای امنیت فیزیکی. | انجام ممیزی وجه نقد و بررسی واریزها برای احراز کامل موجودی نقدی فروشگاه. | انجام یا هدایت بررسی موجودی در پاسخ به نتایج کسری خارج از دامنه قابل قبول. | ارائه توصیه‌ها و راهکارها در وضعیت‌های بحرانی مانند خشونت در محل کار، اعتراض‌ها و تجمعات. | پیشنهاد بهبود در برنامه‌ها، نیروی انسانی، زمان‌بندی یا آموزش پیشگیری از زیان. | بازبینی گزارش‌های استثنای پیشگیری از زیان و مغایرت‌های نقدی برای اطمینان از رعایت دستورالعمل‌ها. | سرپرستی امور نظارت تصویری، کشف یا رسیدگی کیفری مرتبط با پرونده‌های سرقت و جرم. | آموزش کارکنان پیشگیری از زیان، مدیران خرده‌فروشی یا کارکنان فروشگاه در زمینه اقدامات کنترل و پیشگیری از زیان. | احراز استفاده و نگهداری صحیح سامانه‌های امنیت فیزیکی، مانند دوربین مدار بسته، برچسب‌های کالا و آژیرهای سرقت. | بازدید از فروشگاه‌ها برای اطمینان از رعایت سیاست‌ها و رویه‌های شرکت.</t>
         </is>
       </c>
     </row>
@@ -835,42 +835,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wind Energy Operations Managers (مدیران عملیات انرژی بادی)</t>
+          <t>مدیران عملیات انرژی بادی (Wind Energy Operations Managers)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Service Site Manager | Site Manager | Turbine Site Manager | Wind Facilities Manager | Wind Operations Supervisor | Wind Plant Manager | Wind Plant Operations Manager | Wind Site Manager | Wind Site Supervisor | Wind Technician Leader</t>
+          <t>مدیر محل ارائه خدمات | مدیر سایت | مدیر سایت توربین | مدیر تأسیسات بادی | سرپرست عملیات بادی | مدیر نیروگاه بادی | مدیر عملیات نیروگاه بادی | مدیر سایت بادی | سرپرست سایت بادی | سرپرست تکنسین‌های بادی</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار تشخیص کامپیوتری | سیستم CMMS | نرم‌افزار زمان‌بندی کارکنان | Gensuite | IBM Lotus Notes | نرم‌افزار کنترل موجودی | نرم‌افزار شبکه محلی (LAN) | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Enterprise Asset Management eAM | Oracle Primavera Systems | نرم‌افزار PLC | نرم‌افزار SAP | نرم‌افزار SCADA | نرم‌افزار مدیریت زمان و حقوق | نرم‌افزار مرورگر وب | نرم‌افزار کنفرانس وب | WebEx WebOffice | نرم‌افزار شبکه گسترده (WAN)</t>
+          <t>Autodesk AutoCAD | نرم‌افزار تشخیص کامپیوتری | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار زمان‌بندی کارکنان | Gensuite | IBM Lotus Notes | نرم‌افزار کنترل موجودی | نرم‌افزار شبکه محلی LAN | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Enterprise Asset Management eAM | Oracle Primavera Systems | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار SAP | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار مدیریت زمان و حقوق | نرم‌افزار مرورگر وب | نرم‌افزار کنفرانس وب | WebEx WebOffice | نرم‌افزار شبکه گسترده WAN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Active Listening | Reading Comprehension | Speaking | Critical Thinking | Monitoring | Writing | Mathematics | Learning Strategies | Active Learning</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | ریاضیات | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Administration and Management | Mechanical | Engineering and Technology | Public Safety and Security | Personnel and Human Resources | Administrative | Computers and Electronics | Customer and Personal Service | Mathematics | Production and Processing | Telecommunications</t>
+          <t>مدیریت و اداره | مکانیک | مهندسی و فناوری | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | اداری | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | تولید و فرآوری | مخابرات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oral Expression | Speech Recognition | Speech Clarity | Oral Comprehension | Written Comprehension | Written Expression | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Near Vision | Fluency of Ideas | Perceptual Speed | Flexibility of Closure | Far Vision | Selective Attention | Visualization | Category Flexibility | Originality</t>
+          <t>بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | بینایی دور | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment | Contact With Others | Indoors, Environmentally Controlled | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Consequence of Error | Indoors, Not Environmentally Controlled | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | E-Mail | Outdoors, Exposed to All Weather Conditions | Importance of Being Exact or Accurate | Outdoors, Under Cover | Time Pressure | Exposed to Hazardous Conditions | Exposed to High Places | Level of Competition | Written Letters and Memos | Exposed to Very Hot or Cold Temperatures | Exposed to Hazardous Equipment</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | پیامد خطا | محیط داخلی، بدون کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا درست بودن | فضای باز، زیر سقف | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض ارتفاعات بالا | سطح رقابت | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Biofuels Production Managers | Biofuels/Biodiesel Technology and Product Development Managers | Biomass Plant Technicians | Biomass Power Plant Managers | Construction Managers | Electrical Engineers | Energy Engineers, Except Wind and Solar | Geothermal Production Managers | Geothermal Technicians | Hydroelectric Plant Technicians | Hydroelectric Production Managers | Industrial Production Managers | Power Distributors and Dispatchers | Power Plant Operators | Solar Energy Installation Managers | Solar Energy Systems Engineers | Stationary Engineers and Boiler Operators | Wind Energy Development Managers | Wind Energy Engineers | Wind Turbine Service Technicians</t>
+          <t>مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مدیران ساخت‌وساز | مهندسان برق | مهندسان انرژی، به جز باد و خورشید | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مدیران تولید صنعتی | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | مهندسان تاسیسات و اپراتورهای دیگ بخار | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Develop processes or procedures for wind operations, including transitioning from construction to commercial operations. | Develop relationships and communicate with customers, site managers, developers, land owners, authorities, utility representatives, or residents. | Establish goals, objectives, or priorities for wind field operations. | Estimate costs associated with operations, including repairs or preventive maintenance. | Maintain operations records, such as work orders, site inspection forms, or other documentation. | Manage warranty repair or replacement services. | Monitor and maintain records of daily facility operations. | Order parts, tools, or equipment needed to maintain, restore, or improve wind field operations. | Oversee the maintenance of wind field equipment or structures, such as towers, transformers, electrical collector systems, roadways, or other site assets. | Prepare wind field operational budgets. | Provide technical support to wind field customers, employees, or subcontractors. | Recruit or select wind operations employees, contractors, or subcontractors. | Review, negotiate, or approve wind farm contracts. | Supervise employees or subcontractors to ensure quality of work or adherence to safety regulations or policies. | Track and maintain records for wind operations, such as site performance, downtime events, parts usage, or substation events. | Train or coordinate the training of employees in operations, safety, environmental issues, or technical issues.</t>
+          <t>تدوین فرایندها یا رویه‌های عملیات بادی، از جمله گذار از مرحله ساخت به بهره‌برداری تجاری. | ایجاد ارتباط و تعامل با مشتریان، مدیران سایت، توسعه‌دهندگان، مالکان زمین، مقامات، نمایندگان شرکت‌های خدمات عمومی یا ساکنان محلی. | تعیین اهداف کلان، اهداف عملیاتی یا اولویت‌های عملیات مزرعه بادی. | برآورد هزینه‌های مرتبط با بهره‌برداری، از جمله تعمیرات یا نگهداری پیشگیرانه. | نگهداری سوابق عملیاتی، مانند دستور کارها، فرم‌های بازرسی سایت یا سایر مستندات. | مدیریت خدمات تعمیر یا تعویض در دوره ضمانت. | پایش و نگهداری سوابق عملیات روزانه تأسیسات. | سفارش قطعات، ابزار یا تجهیزات لازم برای نگهداری، بازیابی یا بهبود عملیات مزرعه بادی. | نظارت بر نگهداری تجهیزات یا سازه‌های مزرعه بادی، مانند برج‌ها، ترانسفورماتورها، سامانه‌های جمع‌آوری برق، جاده‌های دسترسی یا سایر دارایی‌های سایت. | تهیه بودجه عملیاتی مزرعه بادی. | ارائه پشتیبانی فنی به مشتریان، کارکنان یا پیمانکاران فرعی مزرعه بادی. | جذب یا انتخاب کارکنان، پیمانکاران یا پیمانکاران فرعی عملیات بادی. | بازبینی، مذاکره یا تأیید قراردادهای مزرعه بادی. | سرپرستی کارکنان یا پیمانکاران فرعی برای اطمینان از کیفیت کار یا رعایت مقررات و سیاست‌های ایمنی. | ثبت و نگهداری سوابق عملیات بادی، مانند عملکرد سایت، رویدادهای توقف، مصرف قطعات یا رویدادهای پست برق. | آموزش کارکنان یا هماهنگی آموزش آنان در زمینه عملیات، ایمنی، مسائل محیط‌زیستی یا مسائل فنی.</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wind Energy Development Managers (مدیران توسعه انرژی بادی)</t>
+          <t>مدیران توسعه انرژی بادی (Wind Energy Development Managers)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Business Development Director | Business Development Manager | Development Director | Development Manager | Project Development Leader | Renewable Project Management and Construction Director</t>
+          <t>مدیر توسعه کسب‌وکار | مدیر توسعه کسب‌وکار | مدیر توسعه | مدیر توسعه | راهبر توسعه پروژه | مدیر ارشد مدیریت و ساخت پروژه‌های تجدیدپذیر</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Critical Thinking | Reading Comprehension | Writing | Speaking | Active Listening | Monitoring | Active Learning | Mathematics</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Administration and Management | English Language | Building and Construction | Engineering and Technology | Economics and Accounting | Customer and Personal Service | Design | Mathematics | Computers and Electronics | Mechanical</t>
+          <t>مدیریت و اداره | زبان انگلیسی | ساختمان و ساخت‌وساز | مهندسی و فناوری | اقتصاد و حسابداری | خدمات مشتری و شخصی | طراحی | ریاضیات | رایانه و الکترونیک | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Written Comprehension | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Speech Recognition | Speech Clarity | Oral Expression | Written Expression | Near Vision | Information Ordering | Category Flexibility | Fluency of Ideas | Flexibility of Closure | Mathematical Reasoning | Selective Attention | Number Facility</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | بیان شفاهی | بیان کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | استدلال ریاضی | توجه انتخابی | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Sitting | Contact With Others | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Importance of Being Exact or Accurate | Time Pressure</t>
+          <t>ایمیل | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | فشار زمانی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Architectural and Engineering Managers | Biofuels Production Managers | Biofuels/Biodiesel Technology and Product Development Managers | Biomass Power Plant Managers | Chief Sustainability Officers | Civil Engineers | Construction Managers | Electrical Engineers | Energy Auditors | Energy Engineers, Except Wind and Solar | Geothermal Production Managers | Hydroelectric Production Managers | Project Management Specialists | Solar Energy Installation Managers | Solar Energy Systems Engineers | Solar Sales Representatives and Assessors | Sustainability Specialists | Wind Energy Engineers | Wind Energy Operations Managers | Wind Turbine Service Technicians</t>
+          <t>مدیران معماری و مهندسی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مدیران نیروگاه‌های زیست‌توده | مدیران ارشد پایداری | مهندسان عمران | مدیران ساخت‌وساز | مهندسان برق | بازرسان انرژی | مهندسان انرژی، به جز باد و خورشید | مدیران تولید زمین‌گرمایی | مدیران تولید برق‌آبی | متخصصان مدیریت پروژه | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نمایندگان و ارزیابان فروش تجهیزات خورشیدی | متخصصان پایداری | مهندسان انرژی بادی | مدیران عملیات انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Coordinate or direct development, energy assessment, engineering, or construction activities to ensure that wind project needs and objectives are met. | Create wind energy project plans, including project scope, goals, tasks, resources, schedules, costs, contingencies, or other project information. | Develop scope of work for wind project functions, such as design, site assessment, environmental studies, surveying, or field support services. | Lead or support negotiations involving tax agreements or abatements, power purchase agreements, land use, or interconnection agreements. | Manage site assessments or environmental studies for wind fields. | Manage wind project costs to stay within budget limits. | Prepare or assist in the preparation of applications for environmental, building, or other required permits. | Prepare requests for proposals (RFPs) for wind project construction or equipment acquisition. | Prepare wind project documentation, including diagrams or layouts. | Provide technical support for the design, construction, or commissioning of wind farm projects. | Provide verbal or written project status reports to project teams, management, subcontractors, customers, or owners. | Review civil design, engineering, or construction technical documentation to ensure compliance with applicable government or industrial codes, standards, requirements, or regulations. | Review or evaluate proposals or bids to make recommendations regarding awarding of contracts. | Supervise the work of subcontractors or consultants to ensure quality and conformance to specifications or budgets. | Update schedules, estimates, forecasts, or budgets for wind projects.</t>
+          <t>هماهنگی یا هدایت فعالیت‌های توسعه، ارزیابی انرژی، مهندسی یا ساخت برای اطمینان از تحقق نیازها و اهداف پروژه بادی. | تدوین برنامه‌های پروژه انرژی بادی، شامل دامنه پروژه، اهداف، وظایف، منابع، زمان‌بندی، هزینه‌ها، پیشامدهای احتمالی یا سایر اطلاعات پروژه. | تدوین شرح کار برای بخش‌های پروژه بادی، مانند طراحی، ارزیابی سایت، مطالعات محیط‌زیستی، نقشه‌برداری یا خدمات پشتیبانی میدانی. | راهبری یا پشتیبانی مذاکرات مربوط به توافق‌ها یا معافیت‌های مالیاتی، قراردادهای خرید برق، کاربری زمین یا توافق‌های اتصال به شبکه. | مدیریت ارزیابی‌های سایت یا مطالعات محیط‌زیستی مزارع بادی. | مدیریت هزینه‌های پروژه بادی برای ماندن در چارچوب بودجه. | تهیه یا کمک به تهیه درخواست مجوزهای محیط‌زیستی، ساختمانی یا سایر مجوزهای لازم. | تهیه درخواست پیشنهاد (RFP) برای ساخت پروژه بادی یا تأمین تجهیزات. | تهیه مستندات پروژه بادی، از جمله نمودارها یا نقشه‌های چیدمان. | ارائه پشتیبانی فنی برای طراحی، ساخت یا راه‌اندازی پروژه‌های مزرعه بادی. | ارائه گزارش‌های شفاهی یا کتبی وضعیت پروژه به تیم‌های پروژه، مدیریت، پیمانکاران فرعی، مشتریان یا مالکان. | بازبینی مستندات فنی طراحی عمرانی، مهندسی یا ساخت برای اطمینان از انطباق با آیین‌نامه‌ها، استانداردها، الزامات یا مقررات دولتی یا صنعتی مربوطه. | بازبینی یا ارزیابی پیشنهادها یا مناقصه‌ها برای ارائه توصیه درباره واگذاری قراردادها. | سرپرستی کار پیمانکاران فرعی یا مشاوران برای اطمینان از کیفیت و انطباق با مشخصات یا بودجه. | به‌روزرسانی زمان‌بندی‌ها، برآوردها، پیش‌بینی‌ها یا بودجه پروژه‌های بادی.</t>
         </is>
       </c>
     </row>
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Brownfield Redevelopment Specialists and Site Managers (متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت)</t>
+          <t>متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت (Brownfield Redevelopment Specialists and Site Managers)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brownfield Program Director | Brownfield Program Manager | Brownfield Redevelopment Coordinator | Brownfields Practice Leader | Brownfields Program Coordinator | Brownfields Program Manager | Environmental Practice Leader | Environmental Program Manager | Environmental Quality Division Manager | Environmental Quality Specialist</t>
+          <t>مدیر ارشد برنامه اراضی قهوه‌ای | مدیر برنامه اراضی قهوه‌ای | هماهنگ‌کننده بازتوسعه اراضی قهوه‌ای | راهبر حوزه اراضی قهوه‌ای | هماهنگ‌کننده برنامه اراضی قهوه‌ای | مدیر برنامه اراضی قهوه‌ای | راهبر حوزه محیط‌زیست | مدیر برنامه زیست‌محیطی | مدیر بخش کیفیت محیط‌زیست | کارشناس کیفیت محیط‌زیست</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>برنامه‌های نرم‌افزاری تجاری | نرم‌افزار مدیریت تقویم | نرم‌افزار ESRI ArcGIS | ESRI ArcMap | ESRI ArcView | Linux | Maptek Vulcan | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Word | MineSight | Oracle Database | Oracle Hyperion | PostgreSQL | Python | SAP Business Objects | نرم‌افزار SAP | نرم‌افزار Salesforce | سایت‌های رسانه‌های اجتماعی | SQL | Tableau | نرم‌افزار Tanium | نرم‌افزار مرورگر وب</t>
+          <t>برنامه‌های نرم‌افزاری تجاری | نرم‌افزار مدیریت تقویم | نرم‌افزار ESRI ArcGIS | ESRI ArcMap | ESRI ArcView | Linux | Maptek Vulcan | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Word | MineSight | Oracle Database | Oracle Hyperion | PostgreSQL | Python | SAP Business Objects | نرم‌افزار SAP | نرم‌افزار Salesforce | سایت‌های رسانه‌های اجتماعی | زبان پرس‌وجوی ساختاریافته SQL | Tableau | نرم‌افزار Tanium | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monitoring | Critical Thinking | Speaking | Reading Comprehension | Active Listening | Writing | Mathematics | Active Learning | Learning Strategies | Science</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>English Language | Customer and Personal Service | Law and Government | Administration and Management | Mathematics | Chemistry | Engineering and Technology | Biology</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | مدیریت و اداره | ریاضیات | شیمی | مهندسی و فناوری | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Problem Sensitivity | Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Mathematical Reasoning | Speech Recognition | Speech Clarity | Category Flexibility | Near Vision | Fluency of Ideas | Originality | Far Vision | Visualization | Number Facility | Flexibility of Closure</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | اصالت | بینایی دور | تجسم | توانایی عددی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Deal With External Customers or the Public in General | Written Letters and Memos | Spend Time Sitting | Freedom to Make Decisions | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chief Sustainability Officers | Civil Engineers | Conservation Scientists | Construction Managers | Environmental Compliance Inspectors | Environmental Engineering Technologists and Technicians | Environmental Engineers | Environmental Restoration Planners | Environmental Science and Protection Technicians, Including Health | Environmental Scientists and Specialists, Including Health | Foresters | Government Property Inspectors and Investigators | Hydrologic Technicians | Hydrologists | Industrial Ecologists | Project Management Specialists | Sustainability Specialists | Urban and Regional Planners | Water Resource Specialists | Water/Wastewater Engineers</t>
+          <t>مدیران ارشد پایداری | مهندسان عمران | دانشمندان حفاظت | مدیران ساخت‌وساز | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | جنگل‌بانان | بازرسان و محققان اموال دولتی | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | متخصصان مدیریت پروژه | متخصصان پایداری | برنامه‌ریزان شهری و منطقه‌ای | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Conduct feasibility or cost-benefit studies for environmental remediation projects. | Conduct quantitative risk assessments for human health, environmental, or other risks. | Coordinate on-site activities for environmental cleanup or remediation projects to ensure compliance with environmental laws, standards, regulations, or other requirements. | Coordinate the disposal of hazardous waste. | Design or conduct environmental restoration studies. | Design or implement measures to improve the water, air, and soil quality of military test sites, abandoned mine land, or other contaminated sites. | Design or implement plans for structural demolition and debris removal. | Design or implement plans for surface or ground water remediation. | Develop or implement plans for revegetation of brownfield sites. | Develop or implement plans for the sustainable regeneration of brownfield sites to ensure regeneration of a wider area by providing environmental protection or economic and social benefits. | Estimate costs for environmental cleanup and remediation of land redevelopment projects. | Identify and apply for project funding. | Identify environmental contamination sources. | Inspect sites to assess environmental damage or monitor cleanup progress. | Maintain records of decisions, actions, and progress related to environmental redevelopment projects. | Negotiate contracts for services or materials needed for environmental remediation. | Plan or implement brownfield redevelopment projects to ensure safety, quality, and compliance with applicable standards or requirements. | Prepare and submit permit applications for demolition, cleanup, remediation, or construction projects. | Prepare reports or presentations to communicate brownfield redevelopment needs, status, or progress. | Provide expert witness testimony on issues such as soil, air, or water contamination and associated cleanup measures. | Provide training on hazardous material or waste cleanup procedures and technologies. | Review or evaluate designs for contaminant treatment or disposal facilities. | Review or evaluate environmental remediation project proposals.</t>
+          <t>انجام مطالعات امکان‌سنجی یا هزینه‌فایده برای پروژه‌های پاک‌سازی محیط‌زیستی. | انجام ارزیابی‌های کمّی ریسک برای سلامت انسان، محیط‌زیست یا سایر مخاطرات. | هماهنگی فعالیت‌های میدانی پروژه‌های پاک‌سازی یا احیای محیط‌زیستی برای اطمینان از رعایت قوانین، استانداردها، مقررات یا سایر الزامات محیط‌زیستی. | هماهنگی دفع پسماند خطرناک. | طراحی یا انجام مطالعات احیای محیط‌زیست. | طراحی یا اجرای اقداماتی برای بهبود کیفیت آب، هوا و خاک محل‌های آزمایش نظامی، اراضی معدنی متروکه یا سایر محل‌های آلوده. | طراحی یا اجرای برنامه‌های تخریب سازه‌ای و برداشت نخاله. | طراحی یا اجرای برنامه‌های پاک‌سازی آب‌های سطحی یا زیرزمینی. | تدوین یا اجرای برنامه‌های بازگرداندن پوشش گیاهی در اراضی قهوه‌ای (آلوده متروکه). | تدوین یا اجرای برنامه‌های بازآفرینی پایدار اراضی قهوه‌ای برای اطمینان از احیای پهنه گسترده‌تر از راه حفاظت محیط‌زیستی یا ایجاد منافع اقتصادی و اجتماعی. | برآورد هزینه‌های پاک‌سازی و احیای محیط‌زیستی پروژه‌های بازتوسعه اراضی. | شناسایی منابع تأمین مالی پروژه و درخواست آن. | شناسایی منابع آلودگی محیط‌زیستی. | بازرسی محل‌ها برای ارزیابی آسیب محیط‌زیستی یا پایش پیشرفت پاک‌سازی. | نگهداری سوابق تصمیم‌ها، اقدامات و پیشرفت پروژه‌های بازتوسعه محیط‌زیستی. | مذاکره درباره قراردادهای خدمات یا مواد مورد نیاز پاک‌سازی محیط‌زیستی. | برنامه‌ریزی یا اجرای پروژه‌های بازتوسعه اراضی قهوه‌ای برای تضمین ایمنی، کیفیت و انطباق با استانداردها یا الزامات مربوطه. | تهیه و ارائه درخواست مجوز برای پروژه‌های تخریب، پاک‌سازی، احیا یا ساخت. | تهیه گزارش‌ها یا ارائه‌ها برای انتقال نیازها، وضعیت یا پیشرفت بازتوسعه اراضی قهوه‌ای. | ارائه شهادت کارشناسی در موضوعاتی مانند آلودگی خاک، هوا یا آب و اقدامات پاک‌سازی مرتبط با آن. | ارائه آموزش درباره رویه‌ها و فناوری‌های پاک‌سازی مواد یا پسماند خطرناک. | بازبینی یا ارزیابی طرح‌های تأسیسات تصفیه یا دفع آلاینده‌ها. | بازبینی یا ارزیابی پیشنهادهای پروژه پاک‌سازی محیط‌زیستی.</t>
         </is>
       </c>
     </row>
@@ -1006,42 +1006,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agents and Business Managers of Artists, Performers, and Athletes (نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران)</t>
+          <t>نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران (Agents and Business Managers of Artists, Performers, and Athletes)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Agent | Athlete Marketing Agent | Booker | Booking Agent | Entertainment Specialist | Literary Agent | Print Agent | Talent Agent | Talent Representative | Theatrical Agent</t>
+          <t>نماینده | نماینده بازاریابی ورزشکاران | هماهنگ‌کننده رزرو برنامه | نماینده رزرو برنامه | کارشناس سرگرمی | نماینده ادبی | نماینده امور چاپ | نماینده هنرمندان | نماینده هنرمندان | نماینده امور تئاتر</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | Apple macOS | Avid Technology iNEWS | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Facebook | نرم‌افزار حسابداری مالی | LexisNexis | LinkedIn | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Salesforce Marketing Cloud | نرم‌افزار Salesforce | نرم‌افزار تحلیل آماری | نرم‌افزار برنامه‌ریزی مالیاتی | Twitter | نرم‌افزار ویدئوکنفرانس | نرم‌افزار مرورگر وب | نرم‌افزار سرور وب | Zoom</t>
+          <t>Adobe Photoshop | Apple macOS | Avid Technology iNEWS | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Facebook | نرم‌افزار حسابداری مالی | LexisNexis | LinkedIn | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Salesforce Marketing Cloud | نرم‌افزار Salesforce | نرم‌افزار تحلیل آماری | نرم‌افزار برنامه‌ریزی مالیاتی | Twitter | نرم‌افزار ویدئوکنفرانس | نرم‌افزار مرورگر وب | نرم‌افزار وب سرور | Zoom</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Writing | Active Learning</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Customer and Personal Service | Sales and Marketing | English Language | Administration and Management | Fine Arts | Communications and Media | Administrative | Personnel and Human Resources</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مدیریت و اداره | هنرهای زیبا | ارتباطات و رسانه | اداری | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oral Expression | Oral Comprehension | Written Comprehension | Problem Sensitivity | Speech Recognition | Speech Clarity | Deductive Reasoning | Written Expression | Inductive Reasoning | Near Vision | Information Ordering | Fluency of Ideas | Originality | Category Flexibility</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Telephone Conversations | E-Mail | Contact With Others | Time Pressure | Spend Time Sitting | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Level of Competition | Indoors, Environmentally Controlled | Coordinate or Lead Others in Accomplishing Work Activities</t>
+          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | فشار زمانی | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Advertising Sales Agents | Advertising and Promotions Managers | Art Directors | First-Line Supervisors of Non-Retail Sales Workers | Fundraisers | Fundraising Managers | Market Research Analysts and Marketing Specialists | Marketing Managers | Meeting, Convention, and Event Planners | Personal Financial Advisors | Producers and Directors | Public Relations Managers | Public Relations Specialists | Real Estate Sales Agents | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Securities, Commodities, and Financial Services Sales Agents | Talent Directors | Telemarketers | Writers and Authors</t>
+          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | مدیران هنری | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | جمع‌آوری‌کنندگان کمک مالی | مدیران جمع‌آوری کمک‌های مالی | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مشاوران مالی شخصی | تهیه‌کنندگان و کارگردانان | مدیران روابط عمومی | متخصصان روابط عمومی | نمایندگان فروش املاک | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | مدیران استعداد | بازاریابان تلفنی | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Advise clients on financial and legal matters, such as investments and taxes. | Arrange meetings concerning issues involving their clients. | Collect fees, commissions, or other payments, according to contract terms. | Conduct auditions or interviews to evaluate potential clients. | Confer with clients to develop strategies for their careers, and to explain actions taken on their behalf. | Develop contacts with individuals and organizations, and apply effective strategies and techniques to ensure their clients' success. | Hire trainers or coaches to advise clients on performance matters, such as training techniques or performance presentations. | Keep informed of industry trends and deals. | Manage business and financial affairs for clients, such as arranging travel and lodging, selling tickets, and directing marketing and advertising activities. | Negotiate with managers, promoters, union officials, and other persons regarding clients' contractual rights and obligations. | Obtain information about or inspect performance facilities, equipment, and accommodations to ensure that they meet specifications. | Prepare periodic accounting statements for clients. | Schedule promotional or performance engagements for clients. | Send samples of clients' work and other promotional material to potential employers to obtain auditions, sponsorships, or endorsement deals.</t>
+          <t>ارائه مشاوره به مشتریان در امور مالی و حقوقی، مانند سرمایه‌گذاری و مالیات. | ترتیب دادن جلسات درباره موضوعات مرتبط با مشتریان. | دریافت حق‌الزحمه، کارمزد یا سایر پرداخت‌ها، بر پایه شرایط قرارداد. | برگزاری آزمون هنری یا مصاحبه برای ارزیابی مشتریان بالقوه. | رایزنی با مشتریان برای تدوین راهبردهای شغلی آنان و تشریح اقدامات انجام‌شده از سوی ایشان. | ایجاد ارتباط با افراد و سازمان‌ها و به‌کارگیری راهبردها و فنون مؤثر برای تضمین موفقیت مشتریان. | به‌کارگیری مربیان یا مدرسان برای مشاوره به مشتریان در موضوعات اجرایی، مانند فنون تمرین یا شیوه ارائه اجرا. | آگاه ماندن از روندها و معاملات صنعت. | مدیریت امور تجاری و مالی مشتریان، مانند ترتیب دادن سفر و اقامت، فروش بلیت و هدایت فعالیت‌های بازاریابی و تبلیغات. | مذاکره با مدیران، برگزارکنندگان، مقامات صنفی و سایر افراد درباره حقوق و تعهدات قراردادی مشتریان. | کسب اطلاعات درباره امکانات، تجهیزات و محل اقامت مربوط به اجرا یا بازرسی آن‌ها برای اطمینان از انطباق با مشخصات. | تهیه صورت‌حساب‌های دوره‌ای برای مشتریان. | زمان‌بندی برنامه‌های تبلیغاتی یا اجرایی مشتریان. | ارسال نمونه آثار مشتریان و سایر مواد تبلیغاتی به کارفرمایان بالقوه برای دریافت فرصت آزمون هنری، حمایت مالی یا قرارداد تبلیغاتی.</t>
         </is>
       </c>
     </row>

--- a/data_extactor/batch_10_fa/batch_0006_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0006_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | مدیریت و امور اداری | زبان انگلیسی | امور اداری و دفتری | بازاریابی و فروش | امور اداری و منابع انسانی | روان‌شناسی | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | زبان انگلیسی | اداری | فروش و بازاریابی | پرسنل و منابع انسانی | روان‌شناسی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | سیالی ذهنی | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | دید دور | توان عضلات تنه | به خاطر سپردن</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | بینایی دور | قدرت تنه | حفظ کردن</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان بهداشت عمومی | کاردان‌های تغذیه | کارشناسان و متخصصان تغذیه | مدیران آموزش و مراکز نگهداری خردسالان | فیزیولوژیست‌های ورزشی | مربیان ورزشی و مربیان آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان خدمات شخصی | کارشناسان آموزش بهداشت | تحلیل‌گران مدیریت | مدیران خدمات بهداشتی و درمانی | مشاوران سلامت روان | دستیاران کاردرمانی | کارکنان امور اوقات فراغت و تفریحات | مدرسان دانشگاهی تربیت‌بدنی و علوم ورزشی | درمانگران امور تفریحی و بازپروری ورزشی | مشاوران توانبخشی | مدیران خدمات اجتماعی و عام‌المنفعه | مدیران مراکز آب‌درمانی و اسپا | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>رابطان سلامت و بهورزان | کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | فیزیولوژیست‌های ورزشی | مربیان ورزش و آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | کارشناسان آموزش بهداشت و ارتقای سلامت | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | مشاوران سلامت روان | کمک‌یاران کاردرمانی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی | مدیران مراکز خدمات اسپا و مراقبت‌های زیبایی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>برنامه‌ریزی و تدوین دوره‌ها و برنامه‌های ورزشی و ارتقای تندرستی عموم | نیازسنجی و ارزیابی اثربخشی برنامه‌ها و دوره‌های تندرستی | نظارت بر نگهداری، ایمنی و بهداشت تجهیزات و امکانات ورزشی | مدیریت و راهبری مربیان ورزشی و کارشناسان سلامت و تغذیه | برگزاری دوره‌ها و کارگاه‌های آموزشی برای کارکنان و مربیان | آموزش و نمایش شیوه صحیح کار با دستگاه‌ها و ادوات ورزشی | برنامه‌ریزی غربالگری‌های سلامت و اقدامات پیشگیرانه پزشکی | نظارت بر رویدادها، همایش‌های ورزشی و پویش‌های ارتقای سلامت | تدوین بودجه‌های عملیاتی و پایش هزینه‌های برنامه‌های ورزشی | ارائه مشاوره‌ها و راهنمایی‌های فردی در حوزه سبک زندگی سالم</t>
+          <t>انجام نیازسنجی یا نظرسنجی برای تعیین میزان علاقه به برنامه‌ها، رویدادها یا خدمات سلامتی و تناسب اندام، یا رضایت از آن‌ها. | برگزاری یا تسهیل دوره‌های آموزشی یا سمینارها برای کارکنان حوزه سلامتی و تناسب اندام. | نمایش نحوه صحیح کار با تجهیزات تناسب اندام، مانند دستگاه‌های مقاومتی، دستگاه‌های هوازی، وزنه‌های آزاد یا دستگاه‌های ارزیابی آمادگی جسمانی. | طراحی کلاس‌های تناسب اندام یا سلامتی، مانند یوگا، ایروبیک، تمرینات قدرتی یا ورزش‌های آبی، با اطمینان از تنوع کلاس‌های ارائه‌شده. | تدوین کمپین‌های بازاریابی برای ترویج سبک زندگی سالم یا مشارکت در برنامه‌های تناسب اندام و سلامتی. | تدوین یا هماهنگی برنامه‌ها یا خدمات تناسب اندام و سلامتی. | ارزیابی برنامه‌های تناسب اندام و سلامتی برای تعیین میزان اثربخشی آن‌ها. | تفسیر داده‌های بیمه یا داده‌های حساب بازپرداخت سلامت (HRA) برای تدوین برنامه‌هایی که نیازهای خاص جوامع هدف را برطرف کند. | نگهداری تجهیزات یا تأسیسات ورزشی، یا ترتیب دادن نگهداری آن‌ها. | نگهداری برنامه‌های زمانی، سوابق یا گزارش‌های مرتبط با سلامتی و تناسب اندام. | مدیریت یا نظارت بر تأسیسات ورزشی یا تفریحی، با اطمینان از ایمن و پاکیزه بودن تأسیسات و تجهیزات. | سازماندهی و نظارت بر رویدادهایی مانند دوهای همگانی یا پیاده‌روی‌های سازمان‌یافته. | سازماندهی و نظارت بر برنامه‌های تناسب اندام یا سلامتی، مانند ارائه اطلاعات، اهدای خون یا آموزش کمک‌های اولیه و احیای قلبی‌ریوی (CPR). | سازماندهی و نظارت بر غربالگری‌های سلامت یا سایر اقدامات پیشگیرانه، مانند ماموگرافی، غربالگری فشار خون یا کلسترول، یا واکسیناسیون آنفلوانزا. | تهیه یا اجرای بودجه و برنامه‌های راهبردی، عملیاتی، خرید یا نگهداری. | ارائه پشتیبانی یا مشاوره فردی در زمینه سلامت عمومی یا تغذیه. | پیشنهاد یا تأیید برنامه‌ها و خدمات جدید برای ترویج سلامتی و تناسب اندام، ایجاد درآمد یا کاهش هزینه‌ها. | پاسخ‌گویی به درخواست‌های مشتریان، عموم مردم یا رسانه‌ها برای دریافت اطلاعات درباره برنامه‌ها یا خدمات سلامتی. | انتخاب یا سرپرستی پیمانکاران، مانند مجریان رویدادها یا متخصصان حوزه سلامت، تناسب اندام و سلامتی. | سرپرستی متخصصان تناسب اندام یا سلامتی، مانند مربیان ورزشی، متخصصان تغذیه یا مربیان بهداشت. | تدریس کلاس‌های تناسب اندام برای بهبود قدرت، انعطاف‌پذیری، آمادگی قلبی‌عروقی یا آمادگی جسمانی عمومی شرکت‌کنندگان. | ثبت و پیگیری داده‌های حضور، مشارکت یا عملکرد مرتبط با رویدادهای سلامتی. | پیگیری راهبردها و برنامه‌های مهار هزینه برای ارزیابی اثربخشی آن‌ها. | به‌کارگیری مهارت‌های رایانه‌ای و نرم‌افزارها برای مدیریت وب‌سایت‌ها یا پایگاه‌های داده، انتشار خبرنامه یا برگزاری وبینار.</t>
         </is>
       </c>
     </row>
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | آموزش و تدریس | امور اداری و منابع انسانی | بازاریابی و فروش | ریاضیات | اقتصاد و حسابداری</t>
+          <t>اداری | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | آموزش و پرورش | پرسنل و منابع انسانی | فروش و بازاریابی | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | درک کتبی | سیالی ذهنی | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | ابتکار و اصالت | توجه انتخابی | محاسبات عددی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | درک کتبی | روانی ایده‌ها | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | اصالت | توجه انتخابی | توانایی عددی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پیرایشگران مردانه | کارشناسان خدمات راهنمای مهمانان | مربیان ورزشی و مربیان آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز مراکز قمار | سرپرستان رده‌اول خدمات خانه‌داری و نظافت | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور دفتری و پشتیبانی اداری | سرپرستان رده‌اول کارکنان خدمات شخصی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | مدیران خدمات پذیرایی و غذا | آرایشگران و متخصصان زیبایی پوست و مو | متصدیان پذیرش هتل و مراکز اقامتی | متصدیان رختکن و فضاهای پذیرایی | مدیران اقامتگاه‌ها و هتل‌ها | ماساژورها و ماساژدرمانگران | مسئولان دفاتر و منشی‌های پزشکی | مدیران خدمات بهداشتی و درمانی | متصدیان پذیرش و اطلاع‌رسانی | متخصصان مراقبت از پوست | مدیران آموزش و بهسازی منابع انسانی</t>
+          <t>پیرایشگران مردانه | متصدیان تشریفات و خدمات میهمانان | مربیان ورزش و آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | مدیران خدمات پذیرایی و غذا و نوشیدنی | آرایشگران و متخصصان زیبایی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان رختکن، امانات و اتاق پرو | مدیران هتل و مراکز اقامتی | ماساژدرمانگران | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | مدیران خدمات درمانی و بهداشتی | متصدیان پذیرش و اطلاعات | متخصصان و تکنسین‌های مراقبت از پوست | مدیران آموزش و بهسازی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>برنامه‌ریزی، هدایت و ارتقای خدمات، دوره‌ها و بسته‌های اسپا | نظارت بر رعایت ضوابط و دستورالعمل‌های بهداشتی و ایمنی | تنظیم بودجه، کنترل هزینه‌ها و ثبت تراکنش‌های مالی روزانه | استخدام، مصاحبه و تعیین وظایف و استانداردهای کاری پرسنل | ارزیابی عملکرد کارکنان و آموزش مهارت‌های فنی و رفتاری | هماهنگی و نظارت بر نوبت‌دهی مراجعان و تقویم کاری پرسنل | نظارت بر عملکرد، تعمیر و نگهداری ابزار و تجهیزات تخصصی | کنترل موجودی مواد اولیه و محصولات و ثبت سفارش‌های خرید | رسیدگی به نظرات، درخواست‌ها و شکایات مراجعان | اجرای راهکارهای بازاریابی و فروش خدمات، محصولات و اشتراک‌ها</t>
+          <t>ارزیابی عملکرد کارکنان و ارائه پیشنهاد برای بهبود کار. | بررسی تجهیزات اسپا برای اطمینان از عملکرد صحیح آن‌ها. | هماهنگی برنامه‌های زمانی مجموعه برای بیشینه‌سازی بهره‌برداری و کارایی. | تدوین یا اجرای راهبردهای بازاریابی. | تعیین اهداف خدماتی یا فروش برای کارکنان و راهنمایی آنان در تحقق این اهداف. | هدایت امور نگهداری یا تعمیر تأسیسات. | تعیین بودجه و اهداف مالی اسپا. | آگاه‌سازی کارکنان از شرح وظایف، انتظارات عملکردی، استانداردهای خدمات به مشتری، یا سیاست‌ها و دستورالعمل‌های سازمانی. | انبارگردانی محصولات و سفارش اقلام جدید. | نگهداری پایگاه‌های داده مشتریان. | پایش عملیات برای اطمینان از رعایت استانداردهای بهداشتی، ایمنی یا نظافتی مربوطه. | شرکت در دوره‌های آموزش مداوم برای به‌روز نگه‌داشتن دانش صنعت. | انجام امور حسابداری، مانند ثبت گردش نقدی روزانه، تهیه اسناد واریز بانکی یا تنظیم صورت‌های مالی. | برنامه‌ریزی یا هدایت خدمات و برنامه‌های اسپا. | جذب، مصاحبه یا استخدام کارکنان. | پاسخ‌گویی به پرسش‌ها یا شکایت‌های مشتریان. | زمان‌بندی نوبت مراجعان. | زمان‌بندی کارکنان یا نظارت بر برنامه‌ریزی زمانی آنان. | فروش محصولات، خدمات یا عضویت‌ها. | آموزش کارکنان در زمینه استفاده یا فروش محصولات، برنامه‌ها یا فعالیت‌ها. | احراز صلاحیت کارکنان، از جمله الزامات تحصیلی و گواهی‌نامه‌ای.</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | امور اداری و منابع انسانی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | آموزش و تدریس | رایانه و الکترونیک | حقوق و مقررات دولتی | بازاریابی و فروش | ارتباطات و رسانه</t>
+          <t>مدیریت و اداره | پرسنل و منابع انسانی | زبان انگلیسی | خدمات مشتری و شخصی | اقتصاد و حسابداری | آموزش و پرورش | رایانه و الکترونیک | قانون و دولت | فروش و بازاریابی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | سیالی ذهنی | ابتکار و اصالت | توجه انتخابی | تقسیم توجه میان امور | تجسم فضایی | به خاطر سپردن</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران عامل و مدیران ارشد اجرایی | مدیران کل و مدیران عملیات | مدیران خدمات اداری | مدیران تأسیسات | مدیران مالی | مدیران تولید صنعتی | مدیران تدارکات و خرید | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران منابع انسانی | مدیران آموزش و بهسازی منابع انسانی | مدیران جبران خدمت و مزایا | مدیران بازاریابی | مدیران فروش | مدیران روابط عمومی | مدیران جذب منابع و حامیان مالی | مدیران سامانه‌ها و فناوری اطلاعات | مدیران خدمات بهداشتی و درمانی | مدیران خدمات اجتماعی و عام‌المنفعه | مدیران املاک، مستغلات و تشکل‌های ساختمانی | مدیران طرح‌های ساختمانی و عمرانی</t>
+          <t>مدیران عامل و مدیران ارشد اجرایی | مدیران کل و مدیران عملیات | مدیران خدمات اداری و پشتیبانی | مدیران امور ساختمان و تأسیسات | مدیران امور مالی | مدیران تولید صنعتی | مدیران خرید و تدارکات | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران منابع انسانی | مدیران آموزش و بهسازی | مدیران جبران خدمت و مزایا | مدیران بازاریابی | مدیران فروش | مدیران روابط عمومی | مدیران جذب منابع مالی و حامیان | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران خدمات درمانی و بهداشتی | مدیران خدمات اجتماعی و خدمات مردمی | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مدیران پروژه‌های ساختمانی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>برنامه‌ریزی، هدایت و هماهنگی عملیات اجرایی واحدها و بخش‌های سازمانی | تدوین اهداف، برنامه‌های کلان، خط‌مشی‌ها و رویه‌های عملیاتی | سرپرستی، هماهنگی و نظارت بر فعالیت‌های کارکنان تخصصی و اجرایی | تنظیم، دفاع و نظارت بر اجرای بودجه‌های جاری و سرمایه‌ای | تجزیه‌وتحلیل داده‌های عملیاتی و مالی برای سنجش تحقق اهداف | جذب، گزینش، ارزیابی عملکرد و تصمیم‌گیری درباره ارتقای کارکنان | مذاکره، بازبینی و تأیید قراردادها و خریدهای مربوط به کالا و خدمات | حصول اطمینان از انطباق فرایندها با قوانین جاری و خط‌مشی‌های سازمان | رفع مسائل حساس و بحران‌های عملیاتی و حل اختلافات کارکنان و مراجعان | نمایندگی سازمان در تعامل با ذی‌نفعان، تأمین‌کنندگان و مراجع بیرونی</t>
+          <t>برنامه‌ریزی، هدایت و هماهنگی عملیات سازمان‌ها یا واحدهایی که جداگانه طبقه‌بندی نشده‌اند. | تعیین اهداف کلان، اهداف عملیاتی، سیاست‌ها و رویه‌های اجرایی واحد سازمانی. | هدایت و هماهنگی فعالیت‌های کارکنان سرپرست و متخصص. | تهیه، توجیه و اداره بودجه‌های جاری و سرمایه‌ای. | تجزیه و تحلیل داده‌های عملیاتی و مالی برای ارزیابی عملکرد در برابر اهداف. | جذب، استخدام، آموزش و ارزیابی کارکنان و ارائه پیشنهاد درباره اقدامات پرسنلی. | مذاکره و تأیید قراردادها، توافق‌نامه‌ها و خرید کالاها و خدمات. | حصول اطمینان از رعایت قوانین، مقررات و سیاست‌های سازمانی مربوطه. | تهیه گزارش‌ها و ارائه‌ها برای مدیریت ارشد و هیئت‌های حاکمیتی. | شناسایی فرصت‌های بهبود فرایند و اجرای تغییرات برای افزایش کارایی. | رفع مشکلات عملیاتی ارجاع‌شده، مسائل مشتریان و اختلافات کارکنان. | نمایندگی سازمان در تعامل با مشتریان، تأمین‌کنندگان و نهادهای بیرونی. | پایش روندهای صنعت و فعالیت رقبا برای پشتیبانی از تصمیم‌های برنامه‌ریزی. | هدایت تخصیص کارکنان، تجهیزات و امکانات میان پروژه‌ها.</t>
         </is>
       </c>
     </row>
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>نگارش | درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | مدیریت و امور اداری | زیست‌شناسی | آموزش و تدریس | امور اداری و دفتری | شیمی</t>
+          <t>زبان انگلیسی | قانون و دولت | مدیریت و اداره | زیست‌شناسی | آموزش و پرورش | اداری | شیمی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | سیالی ذهنی | ابتکار و اصالت | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>بیان کتبی | درک کتبی | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران عامل و مدیران ارشد اجرایی | مدیران پایداری و محیط‌زیست | مدیران داده‌های بالینی | مدیران تطبیق و نظارت مقرراتی | کارشناسان امور انطباق مقرراتی | بازرسان انطباق زیست‌محیطی | متخصصان و کارشناسان محیط‌زیست، از جمله بهداشت | ممیزان و بازرسان مالی | متخصصان ریسک مالی | بازرسان و محققان اموال دولتی | فناوران اطلاعات سلامت و متصدیان ثبت پزشکی | مهندسان ایمنی و بهداشت، به‌جز مهندسی معدن | تحلیل‌گران مدیریت | مدیران خدمات بهداشتی و درمانی | مدیران علوم پایه و طبیعی | کارشناسان مدیریت پروژه | مدیران روابط عمومی | مدیران سیستم‌های کنترل کیفیت | کارشناسان امور انطباق مقرراتی و حقوقی صنایع</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران عامل و مدیران ارشد اجرایی | مدیران ارشد پایداری سازمانی | مدیران داده‌های بالینی | مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | بازرسان و ارزیابان مالی | کارشناسان ریسک مالی | بازرسان و ممیزان اموال دولتی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | مدیران علوم طبیعی و پایه‌ای | کارشناسان مدیریت پروژه | مدیران روابط عمومی | مدیران سیستم‌های کنترل کیفیت | کارشناسان امور رگولاتوری و انطباق مقرراتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>تدوین راهبردها و برنامه‌های اجرایی اخذ مجوز و ثبت محصولات جدید | نظارت بر تهیه، تدوین و ارسال مستندات، پرونده‌ها و گزارش‌ها به مراجع صدور پروانه | بازبینی کلیه اسناد تنظیمی از حیث صحت، کفایت فنی و انطباق با قوانین | ابلاغ الزامات مراجع ذی‌صلاح به واحدهای سازمانی و تفسیر دستورالعمل‌ها | نمایندگی سازمان در تعامل با مراجع قانونی و ناظران ملی و بین‌المللی | تدوین، بازنگری و استقرار روش‌های اجرایی استاندارد (SOP) و شیوه‌نامه‌های کاری | پایش مستمر تغییرات قوانین، بخشنامه‌ها و روندهای مقرراتی حاکم بر صنعت | مدیریت و هماهنگی فرایندهای ممیزی، بازرسی‌های قانونی و فراخوان محصولات | ارائه مشاوره‌های مقرراتی به تیم‌های تحقیق‌وتوسعه، تولید و بازاریابی | آموزش کارکنان درباره خط‌مشی‌ها، آیین‌نامه‌ها و الزامات حقوقی و نظارتی</t>
+          <t>انتقال اطلاعات نظارتی به واحدهای مختلف و حصول اطمینان از تفسیر صحیح این اطلاعات. | مشارکت در تدوین یا اجرای برنامه‌های راهبردی و عملیاتی واحد کسب‌وکار. | هماهنگی فرایندهای کشف اسناد و اخذ اظهارات داخلی با کارکنان واحد حقوقی. | تدوین و نگهداری رویه‌های اجرایی استاندارد یا شیوه‌های کاری محلی. | تدوین راهبردهای نظارتی و برنامه‌های اجرایی برای تهیه و ارائه پرونده محصولات جدید. | برقراری ارتباط با نهادهای نظارتی محیط‌زیستی ایالتی یا فدرال برای آگاهی از پیامدهای احتمالی مقررات پیشنهادی محیط‌زیستی و تحلیل آن‌ها. | هدایت امور مستندسازی برای حصول اطمینان از رعایت مقررات و استانداردهای داخلی و بین‌المللی. | هدایت تهیه و ارائه درخواست‌ها، گزارش‌ها یا مکاتبات مربوط به نهادهای نظارتی. | استقرار رویه‌ها یا سامانه‌هایی برای انتشار اسناد ارسالی به‌صورت چاپی یا الکترونیکی. | تعیین اولویت‌ها یا بودجه امور نظارتی و تخصیص منابع و حجم کار. | ارزیابی سامانه‌های جدید انتشار نرم‌افزاری و رایزنی با نهادهای نظارتی درباره اخبار یا به‌روزرسانی‌های انتشار الکترونیکی اسناد. | ارزیابی جنبه‌های سبز امور نظارتی، مانند استفاده از مواد سمی در بسته‌بندی، مسائل ردپای کربن، یا اجرای سیاست‌های سبز. | تدوین یا اجرای سیاست‌ها و رویه‌های امور نظارتی برای حفظ یا ارتقای انطباق با مقررات. | اجرا یا پایش سامانه‌های رسیدگی به شکایات برای حصول اطمینان از رسیدگی مؤثر و به‌موقع به همه شکایات. | بررسی شکایت‌های مربوط به محصول و تهیه مستندات و پرونده‌های لازم برای ارائه به نهادهای نظارتی ذی‌ربط. | به‌روز نگه‌داشتن دانش مقررات مربوطه، از جمله مقررات پیشنهادی و نهایی. | مدیریت فعالیت‌هایی مانند ممیزی، بازرسی نهادهای نظارتی یا فراخوان جمع‌آوری محصول. | پایش روندهای نوظهور مقررات صنعت برای تعیین پیامدهای احتمالی آن بر فرایندهای سازمان. | پایش فعالیت‌های امور نظارتی برای اطمینان از همسویی آن‌ها با ابتکارهای پایداری یا سبز شرکت. | پایش روندهای امور نظارتی مرتبط با مسائل محیط‌زیستی. | مشارکت در تدوین یا اجرای پروتکل‌های کارآزمایی بالینی. | ارائه راهنمایی نظارتی به واحدها یا تیم‌های پروژه توسعه در زمینه طراحی، توسعه، ارزیابی یا بازاریابی محصولات. | ارائه پاسخ به نهادهای نظارتی درباره اطلاعات یا مسائل محصول. | نمایندگی سازمان نزد نهادهای نظارتی داخلی یا بین‌المللی در موضوعات یا تصمیم‌های مهم سیاستی مرتبط با محصولات شرکت. | بازبینی همه مدارک ارسالی به نهادهای نظارتی برای اطمینان از به‌موقع بودن، دقت، جامعیت یا انطباق با استانداردهای نظارتی. | بازبینی مدارکی مانند ادبیات بازاریابی یا راهنمای کاربر برای اطمینان از رعایت الزامات نهادهای نظارتی. | آموزش کارکنان در زمینه سیاست‌ها یا رویه‌های نظارتی.</t>
         </is>
       </c>
     </row>
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | امور اداری و منابع انسانی | رایانه و الکترونیک | آموزش و تدریس | امور اداری و دفتری | ایمنی و امنیت عمومی</t>
+          <t>قانون و دولت | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | رایانه و الکترونیک | آموزش و پرورش | اداری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان کتبی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | سیالی ذهنی | دید دور</t>
+          <t>بیان کتبی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران عامل و مدیران ارشد اجرایی | متخصصان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان امور انطباق مقرراتی | متخصصان مدیریت اسناد | بازرسان انطباق زیست‌محیطی | ممیزان و بازرسان مالی | متخصصان ریسک مالی | ممیزان، بازرسان و تحلیل‌گران بررسی تقلب | بازرسان و محققان اموال دولتی | فناوران اطلاعات سلامت و متصدیان ثبت پزشکی | مهندسان ایمنی و بهداشت، به‌جز مهندسی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت | مدیران امور انطباق مقرراتی و حقوقی صنایع | کارشناسان امور انطباق مقرراتی و حقوقی صنایع | متخصصان پیشگیری از کسری و هدررفت کالا | متخصصان مدیریت امنیت | مدیران حراست و حفاظت فیزیکی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران عامل و مدیران ارشد اجرایی | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان مدیریت اسناد و مدارک | بازرسان رعایت ضوابط زیست‌محیطی | بازرسان و ارزیابان مالی | کارشناسان ریسک مالی | کارشناسان بازرسی، کشف و تحلیل تقلب | بازرسان و ممیزان اموال دولتی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | مدیران امور انطباق مقرراتی و حقوقی صنایع | کارشناسان امور رگولاتوری و انطباق مقرراتی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>برنامه‌ریزی، هدایت و اجرای شیوه‌نامه‌ها و خط‌مشی‌های انطباق مقرراتی در سازمان | طراحی و اجرای نظارت‌های دوره‌ای و ممیزی‌های داخلی انطباق با استانداردها | هدایت تحقیقات و رسیدگی‌های داخلی به تخلفات و انحرافات قانونی و اداری | شناسایی و ارزیابی ریسک‌های عدم انطباق و تدوین راهکارهای کنترل ریسک | نظارت بر سامانه‌های گزارش‌دهی داخلی، سوت‌زنی و پیگیری شکایات | ارائه گزارش‌های عملکردی و تحلیلی وضعیت انطباق به هیئت‌مدیره و مراجع نظارتی | تدوین و اجرای برنامه‌های آموزشی پیرامون قوانین، اخلاق حرفه‌ای و مقررات | بررسی مستندات بازاریابی و قراردادها برای تطابق با قوانین حاکم | همکاری با ممیزان و بازرسان مستقل بیرونی در فرآیندهای حسابرسی و بازرسی | اصلاح و بازنگری رویه‌های سازمانی متناسب با تغییرات مقرراتی و قانونی</t>
+          <t>ارائه مشاوره به مدیریت داخلی یا شرکای تجاری درباره اجرا یا اداره برنامه‌های انطباق. | ارائه مشاوره به متخصصان فنی درباره تدوین یا استفاده از ابزارهای انطباق یا گزارش‌دهی محیط‌زیستی. | همکاری با واحدهای منابع انسانی برای حصول اطمینان از اجرای یکسان راهبردهای اقدام انضباطی در موارد نقض استانداردهای انطباق. | انجام ممیزی‌های محیط‌زیستی برای اطمینان از رعایت استانداردهای محیط‌زیستی. | انجام یا هدایت تحقیقات داخلی درباره مسائل انطباق. | انجام بازبینی‌ها یا ممیزی‌های داخلی دوره‌ای برای اطمینان از رعایت رویه‌های انطباق. | رایزنی با وکلای شرکت در صورت لزوم برای رسیدگی به مسائل دشوار انطباق حقوقی. | طراحی یا اجرای بهبودها در اطلاع‌رسانی، پایش یا اعمال استانداردهای انطباق. | تدوین راهبردهای مدیریت ریسک بر پایه ارزیابی ریسک‌های محصول، انطباق یا عملیات. | هدایت برنامه‌های محیط‌زیستی، مانند انطباق هوا یا آب، مخازن ذخیره روزمینی یا زیرزمینی، پیشگیری یا مهار نشت، مدیریت پسماند یا مواد خطرناک، بازیافت پسماند جامد، مدیریت پسماند پزشکی، کیفیت هوای داخلی، مدیریت تلفیقی آفات، آموزش کارکنان، یا آمادگی در برابر بلایا. | هدایت تدوین یا اجرای سیاست‌ها و رویه‌های مرتبط با انطباق در سراسر سازمان. | بحث درباره مسائل نوظهور انطباق برای حصول اطمینان از آگاهی مدیریت و کارکنان از سامانه‌ها، سیاست‌ها و شیوه‌های گزارش‌دهی انطباق. | انتشار سیاست‌ها و رویه‌های مکتوب مرتبط با فعالیت‌های انطباق. | ارزیابی رویه‌های آزمون برای برآورده کردن مشخصات برنامه‌های پایش محیط‌زیستی. | ارائه گزارش‌های انطباق مقتضی به نهادهای نظارتی. | شناسایی مسائل انطباق که نیازمند پیگیری یا بررسی هستند. | آگاه ماندن از تغییرات، روندها یا بهترین شیوه‌های در پیش روی صنعت. | نگهداری مستندات فعالیت‌های انطباق، مانند شکایت‌های دریافت‌شده یا نتایج بررسی‌ها. | پایش سامانه‌های انطباق برای اطمینان از اثربخشی آن‌ها. | نظارت بر سامانه‌های گزارش‌دهی داخلی، مانند خطوط تلفن گزارش تخلف شرکت. | تهیه گزارش‌های مدیریتی درباره عملیات و پیشرفت امور انطباق. | ارائه کمک به ممیزان داخلی یا خارجی در بازبینی‌های انطباق. | ارائه آموزش به کارکنان در موضوعات، سیاست‌ها یا رویه‌های مرتبط با انطباق. | گزارش موارد نقض استانداردهای انطباق یا مقررات به نهادهای اجرایی دارای صلاحیت، در صورت لزوم یا الزام. | بازبینی اطلاع‌رسانی‌هایی مانند تبلیغات فروش اوراق بهادار برای اطمینان از نبود نقض استانداردها یا مقررات. | بازبینی یا اصلاح سیاست‌ها یا دستورالعمل‌های اجرایی برای انطباق با تغییرات استانداردها یا مقررات محیط‌زیستی. | ایفای نقش به‌عنوان مرجع تماس محرمانه برای کارکنان جهت ارتباط با مدیریت، شفاف‌سازی مسائل یا دوراهی‌ها، یا گزارش تخلفات. | احراز اینکه همه سیاست‌ها و رویه‌های نظارتی مستند، اجرا و اطلاع‌رسانی شده‌اند. | احراز اینکه فناوری نرم‌افزاری لازم برای نظارت و پایش کافی در همه حوزه‌های الزامی مستقر است.</t>
         </is>
       </c>
     </row>
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | مدیریت و امور اداری | زبان انگلیسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | روان‌شناسی | رایانه و الکترونیک | امور اداری و منابع انسانی | ریاضیات | امور اداری و دفتری</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | مدیریت و اداره | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | پرسنل و منابع انسانی | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | دید نزدیک | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ابتکار و اصالت | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | دید دور | مرتب‌سازی اطلاعات | سیالی ذهنی | انعطاف‌پذیری نتیجه‌گیری</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان تداوم کسب‌وکار | متخصصان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران تطبیق و نظارت مقرراتی | مدیران مدیریت بحران | بازرسان انطباق زیست‌محیطی | متخصصان ریسک مالی | سرپرستان رده‌اول نیروهای حراست و انتظامات | ممیزان، بازرسان و تحلیل‌گران بررسی تقلب | مهندسان ایمنی و بهداشت، به‌جز مهندسی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت | مدیران خدمات بهداشتی و درمانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های ایمنی و بهداشت حرفه‌ای | کارآگاهان و محققان خصوصی | متخصصان پیشگیری از کسری و هدررفت کالا | متخصصان مدیریت امنیت | مدیران حراست و حفاظت فیزیکی | مدیران خدمات اجتماعی و عام‌المنفعه</t>
+          <t>کارشناسان برنامه‌ریزی تداوم کسب‌وکار | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران تطبیق و نظارت مقرراتی | مدیران مدیریت بحران و پدافند غیرعامل | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان ریسک مالی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان بازرسی، کشف و تحلیل تقلب | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | کارآگاهان و بازرسان خصوصی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>تدوین و اجرای برنامه‌ها و دستورالعمل‌های کاهش ضایعات و صیانت از کالا | ارزیابی ریسک‌های امنیتی شعب و انبارها و تخصیص نیروها و تجهیزات لازم | هدایت تحقیقات داخلی درباره سرقت‌های اداری، تبانی، تقلب و تخلفات | همکاری با نهادهای انتظامی و قضایی برای پیگیری پرونده‌های سرقت و جعل | نظارت بر نصب، کارکرد و نگهداری سیستم‌های نظارت تصویری و دزدگیرها | تحلیل داده‌های انبار و فروش برای شناسایی مغایرت‌ها و الگوهای کسری | برنامه‌ریزی و هدایت ممیزی‌های ایمنی، انبارگردانی و مغایرت‌های مالی | بازرسی‌های سرزده و دوره‌ای از فروشگاه‌ها و مراکز توزیع | تدوین و اجرای دوره‌های آموزشی پیشگیری از زیان و کنترل موجودی برای کارکنان | مدیریت شرایط بحرانی نظیر خشونت در محیط کار و سرقت‌های سازمان‌یافته</t>
+          <t>اداره سامانه‌ها و برنامه‌های کاهش زیان، کنترل موجودی یا افزایش ایمنی. | ارائه مشاوره به واحدهای خرده‌فروشی درباره تدوین رویه‌های بررسی زیان. | ارائه مشاوره به مدیران خرده‌فروشی درباره رعایت آیین‌نامه‌ها، قوانین، مقررات یا استانداردهای مربوطه. | تجزیه و تحلیل داده‌های خرده‌فروشی برای شناسایی روندهای جاری یا نوظهور سرقت و تقلب. | ارزیابی نیازهای امنیتی در همه شعب برای اطمینان از استقرار درست منابع پیشگیری از زیان، مانند نیروی انسانی و فناوری. | همکاری با نیروهای انتظامی برای بررسی و حل پرونده‌های سرقت یا تقلب بیرونی. | هماهنگی یا انجام تحقیقات داخلی درباره مشکلاتی مانند سرقت کارکنان و نقض سیاست‌های پیشگیری از زیان شرکت. | هماهنگی تحقیقات سرقت و تقلب مرتبط با مجرمان حرفه‌ای یا فعالیت‌های گروهی سازمان‌یافته. | ایجاد و حفظ همکاری با نهادهای انتظامی فدرال، ایالتی یا محلی یا اعضای جامعه پیشگیری از زیان در خرده‌فروشی. | هدایت نصب تجهیزات نظارت پنهان، مانند دوربین‌های امنیتی. | هدایت برنامه‌های ممیزی پیشگیری از زیان، شامل ممیزی فروشگاه‌های هدف، ممیزی نگهداری، ممیزی ایمنی یا ممیزی سامانه‌های الکترونیکی نظارت بر کالا (EAS). | استخدام یا سرپرستی کارکنان پیشگیری از زیان. | شناسایی احتمال بروز زیان و تدوین راهبردهایی برای حذف آن. | بررسی یا مصاحبه با افراد مظنون به سرقت از فروشگاه یا سرقت داخلی. | نگهداری پایگاه‌های داده مانند سوابق چک‌های برگشتی، گزارش‌های متخلفان مکرر و فهرست فعال‌سازی آژیرها. | نگهداری مستندات همه فعالیت‌های پیشگیری از زیان. | پایش و بازبینی رویه‌ها و سامانه‌های اسناد اداری برای پیشگیری از کسری‌های ناشی از خطا. | پایش رعایت رویه‌های عملیاتی، ایمنی یا کنترل موجودی، از جمله استانداردهای امنیت فیزیکی. | انجام ممیزی وجه نقد و بررسی واریزها برای احراز کامل موجودی نقدی فروشگاه. | انجام یا هدایت بررسی موجودی در پاسخ به نتایج کسری خارج از دامنه قابل قبول. | ارائه توصیه‌ها و راهکارها در وضعیت‌های بحرانی مانند خشونت در محل کار، اعتراض‌ها و تجمعات. | پیشنهاد بهبود در برنامه‌ها، نیروی انسانی، زمان‌بندی یا آموزش پیشگیری از زیان. | بازبینی گزارش‌های استثنای پیشگیری از زیان و مغایرت‌های نقدی برای اطمینان از رعایت دستورالعمل‌ها. | سرپرستی امور نظارت تصویری، کشف یا رسیدگی کیفری مرتبط با پرونده‌های سرقت و جرم. | آموزش کارکنان پیشگیری از زیان، مدیران خرده‌فروشی یا کارکنان فروشگاه در زمینه اقدامات کنترل و پیشگیری از زیان. | احراز استفاده و نگهداری صحیح سامانه‌های امنیت فیزیکی، مانند دوربین مدار بسته، برچسب‌های کالا و آژیرهای سرقت. | بازدید از فروشگاه‌ها برای اطمینان از رعایت سیاست‌ها و رویه‌های شرکت.</t>
         </is>
       </c>
     </row>
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | ریاضیات | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | ریاضیات | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | مکانیک | فنی و مهندسی | ایمنی و امنیت عمومی | امور اداری و منابع انسانی | امور اداری و دفتری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ریاضیات | تولید و فراوری | مخابرات</t>
+          <t>مدیریت و اداره | مکانیک | مهندسی و فناوری | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | اداری | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | تولید و فرآوری | مخابرات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | دید نزدیک | سیالی ذهنی | سرعت ادراک | انعطاف‌پذیری نتیجه‌گیری | دید دور | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت</t>
+          <t>بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار | بینایی دور | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران تولید سوخت‌های زیستی | مدیران توسعه فناوری و محصولات سوخت زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مدیران طرح‌های ساختمانی و عمرانی | مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران تولید نیروگاه برق‌آبی | مدیران تولید صنعتی | توزیع‌کنندگان و دیسپچرهای شبکه برق | متصدیان اتاق کنترل نیروگاه | مدیران نصب تأسیسات خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | تکنسین‌ها و بهره‌برداران دیگ‌های بخار و تأسیسات حرارتی | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی بادی | تکنسین‌های خدمات و تعمیرات توربین‌های بادی</t>
+          <t>مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مدیران پروژه‌های ساختمانی | مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | مدیران تولید صنعتی | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی باد | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>تدوین دستورالعمل‌های بهره‌برداری و انتقال از فاز ساخت به فاز تجاری | نظارت بر عملیات نگهداری پیشگیرانه و تعمیرات توربین‌ها، پست‌ها و خطوط انتقال | نظارت بر رعایت کامل ضوابط ایمنی، بهداشت کار و الزامات زیست‌محیطی | پایش مستمر شاخص‌های عملکردی سایت، ضریب دسترسی و کاهش توقفات فنی | تدوین و مدیریت بودجه‌های عملیاتی، تعمیراتی و برآورد هزینه‌ها | سرپرستی، ارزیابی و آموزش مستمر تکنسین‌ها و پیمانکاران فنی | تأمین قطعات یدکی حیاتی، ابزارآلات و تجهیزات موردنیاز مزرعه بادی | رسیدگی به تعهدات گارانتی، پیگیری دعاوی فنی و عیب‌یابی تجهیزات اصلی | هماهنگی و مذاکره با کارفرما، شبکه دیسپاچینگ برق و پیمانکاران جانبی | ثبت دقیق سوابق تعمیراتی، سفارش‌های کاری و گزارش‌های توقف نیروگاه</t>
+          <t>تدوین فرایندها یا رویه‌های عملیات بادی، از جمله گذار از مرحله ساخت به بهره‌برداری تجاری. | ایجاد ارتباط و تعامل با مشتریان، مدیران سایت، توسعه‌دهندگان، مالکان زمین، مقامات، نمایندگان شرکت‌های خدمات عمومی یا ساکنان محلی. | تعیین اهداف کلان، اهداف عملیاتی یا اولویت‌های عملیات مزرعه بادی. | برآورد هزینه‌های مرتبط با بهره‌برداری، از جمله تعمیرات یا نگهداری پیشگیرانه. | نگهداری سوابق عملیاتی، مانند دستور کارها، فرم‌های بازرسی سایت یا سایر مستندات. | مدیریت خدمات تعمیر یا تعویض در دوره ضمانت. | پایش و نگهداری سوابق عملیات روزانه تأسیسات. | سفارش قطعات، ابزار یا تجهیزات لازم برای نگهداری، بازیابی یا بهبود عملیات مزرعه بادی. | نظارت بر نگهداری تجهیزات یا سازه‌های مزرعه بادی، مانند برج‌ها، ترانسفورماتورها، سامانه‌های جمع‌آوری برق، جاده‌های دسترسی یا سایر دارایی‌های سایت. | تهیه بودجه عملیاتی مزرعه بادی. | ارائه پشتیبانی فنی به مشتریان، کارکنان یا پیمانکاران فرعی مزرعه بادی. | جذب یا انتخاب کارکنان، پیمانکاران یا پیمانکاران فرعی عملیات بادی. | بازبینی، مذاکره یا تأیید قراردادهای مزرعه بادی. | سرپرستی کارکنان یا پیمانکاران فرعی برای اطمینان از کیفیت کار یا رعایت مقررات و سیاست‌های ایمنی. | ثبت و نگهداری سوابق عملیات بادی، مانند عملکرد سایت، رویدادهای توقف، مصرف قطعات یا رویدادهای پست برق. | آموزش کارکنان یا هماهنگی آموزش آنان در زمینه عملیات، ایمنی، مسائل محیط‌زیستی یا مسائل فنی.</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | شنیدن فعال | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | زبان انگلیسی | ساختمان و ساخت‌وساز | فنی و مهندسی | اقتصاد و حسابداری | خدمات مشتریان و خدمات فردی | طراحی | ریاضیات | رایانه و الکترونیک | مکانیک</t>
+          <t>مدیریت و اداره | زبان انگلیسی | ساختمان و ساخت‌وساز | مهندسی و فناوری | اقتصاد و حسابداری | خدمات مشتری و شخصی | طراحی | ریاضیات | رایانه و الکترونیک | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | بیان شفاهی | بیان کتبی | دید نزدیک | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | سیالی ذهنی | انعطاف‌پذیری نتیجه‌گیری | استدلال ریاضی | توجه انتخابی | محاسبات عددی</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | بیان شفاهی | بیان کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | استدلال ریاضی | توجه انتخابی | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران فنی و مهندسی و معماری | مدیران تولید سوخت‌های زیستی | مدیران توسعه فناوری و محصولات سوخت زیستی | مدیران نیروگاه‌های زیست‌توده | مدیران پایداری و محیط‌زیست | مهندسان عمران | مدیران طرح‌های ساختمانی و عمرانی | مهندسان برق | ممیزان انرژی | مهندسان انرژی، به‌جز بادی و خورشیدی | مدیران تولید انرژی زمین‌گرمایی | مدیران تولید نیروگاه برق‌آبی | کارشناسان مدیریت پروژه | مدیران نصب تأسیسات خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | متخصصان توسعه پایدار | مهندسان انرژی بادی | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی | تکنسین‌های خدمات و تعمیرات توربین‌های بادی</t>
+          <t>مدیران فنی و مهندسی و معماری | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | مدیران نیروگاه‌های زیست‌توده | مدیران ارشد پایداری سازمانی | مهندسان عمران | مدیران پروژه‌های ساختمانی | مهندسان برق | ممیزان انرژی | مهندسان انرژی، به‌جز بادی و خورشیدی | مدیران تولید انرژی زمین‌گرمایی | مدیران تولید نیروگاه‌های برق‌آبی | کارشناسان مدیریت پروژه | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | کارشناسان پایداری و توسعه پایدار | مهندسان انرژی باد | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>تدوین برنامه جامع پروژه مشتمل بر محدوده، اهداف، منابع، زمان‌بندی و بودجه | مدیریت مطالعات پتانسیل‌سنجی باد و ارزیابی‌های زیست‌محیطی سایت‌های احداث | تهیه، تنظیم و پیگیری مدارک اخذ پروانه‌ها و مجوزهای قانونی ساخت و بهره‌برداری | مذاکره و تنظیم قراردادهای اتصال به شبکه، خرید تضمینی برق (PPA) و تملک اراضی | تهیه اسناد مناقصه (RFP) برای احداث نیروگاه و خرید تجهیزات توربین‌ها | ارزیابی پیشنهادها و پروپوزال‌های فنی و مالی ارائه‌شده در مناقصات | کنترل هزینه‌های طرح متناسب با بودجه مصوب و پیش‌بینی جریانات نقدی | نظارت بر عملکرد مشاوران و پیمانکاران مهندسی و عمرانی در فاز اجرا | بررسی اسناد فنی مهندسی و نقشه‌ها جهت تطابق با استانداردها و آیین‌نامه‌ها | ارائه گزارش‌های دوره‌ای از پیشرفت فیزیکی و مالی طرح به ذی‌نفعان و سرمایه‌گذاران</t>
+          <t>هماهنگی یا هدایت فعالیت‌های توسعه، ارزیابی انرژی، مهندسی یا ساخت برای اطمینان از تحقق نیازها و اهداف پروژه بادی. | تدوین برنامه‌های پروژه انرژی بادی، شامل دامنه پروژه، اهداف، وظایف، منابع، زمان‌بندی، هزینه‌ها، پیشامدهای احتمالی یا سایر اطلاعات پروژه. | تدوین شرح کار برای بخش‌های پروژه بادی، مانند طراحی، ارزیابی سایت، مطالعات محیط‌زیستی، نقشه‌برداری یا خدمات پشتیبانی میدانی. | راهبری یا پشتیبانی مذاکرات مربوط به توافق‌ها یا معافیت‌های مالیاتی، قراردادهای خرید برق، کاربری زمین یا توافق‌های اتصال به شبکه. | مدیریت ارزیابی‌های سایت یا مطالعات محیط‌زیستی مزارع بادی. | مدیریت هزینه‌های پروژه بادی برای ماندن در چارچوب بودجه. | تهیه یا کمک به تهیه درخواست مجوزهای محیط‌زیستی، ساختمانی یا سایر مجوزهای لازم. | تهیه درخواست پیشنهاد (RFP) برای ساخت پروژه بادی یا تأمین تجهیزات. | تهیه مستندات پروژه بادی، از جمله نمودارها یا نقشه‌های چیدمان. | ارائه پشتیبانی فنی برای طراحی، ساخت یا راه‌اندازی پروژه‌های مزرعه بادی. | ارائه گزارش‌های شفاهی یا کتبی وضعیت پروژه به تیم‌های پروژه، مدیریت، پیمانکاران فرعی، مشتریان یا مالکان. | بازبینی مستندات فنی طراحی عمرانی، مهندسی یا ساخت برای اطمینان از انطباق با آیین‌نامه‌ها، استانداردها، الزامات یا مقررات دولتی یا صنعتی مربوطه. | بازبینی یا ارزیابی پیشنهادها یا مناقصه‌ها برای ارائه توصیه درباره واگذاری قراردادها. | سرپرستی کار پیمانکاران فرعی یا مشاوران برای اطمینان از کیفیت و انطباق با مشخصات یا بودجه. | به‌روزرسانی زمان‌بندی‌ها، برآوردها، پیش‌بینی‌ها یا بودجه پروژه‌های بادی.</t>
         </is>
       </c>
     </row>
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | علوم تجربی و آزمایشگاهی</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | مدیریت و امور اداری | ریاضیات | شیمی | فنی و مهندسی | زیست‌شناسی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | مدیریت و اداره | ریاضیات | شیمی | مهندسی و فناوری | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | سیالی ذهنی | ابتکار و اصالت | دید دور | تجسم فضایی | محاسبات عددی | انعطاف‌پذیری نتیجه‌گیری</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | اصالت | بینایی دور | تجسم | توانایی عددی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران پایداری و محیط‌زیست | مهندسان عمران | کارشناسان حفاظت از منابع طبیعی | مدیران طرح‌های ساختمانی و عمرانی | بازرسان انطباق زیست‌محیطی | فناوران و تکنسین‌های مهندسی محیط‌زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیا و بازیابی زیست‌محیطی | تکنسین‌های علوم زیست‌محیطی و بهداشت عمومی | متخصصان و کارشناسان محیط‌زیست، از جمله بهداشت | جنگل‌داران | بازرسان و محققان اموال دولتی | تکنسین‌های هیدرولوژی و آب‌شناسی | هیدرولوژیست‌ها و متخصصان منابع آب | بوم‌شناسان صنعتی | کارشناسان مدیریت پروژه | متخصصان توسعه پایدار | برنامه‌ریزان شهری و منطقه‌ای | کارشناسان منابع آب | مهندسان آب و فاضلاب</t>
+          <t>مدیران ارشد پایداری سازمانی | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | مدیران پروژه‌های ساختمانی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کارشناسان جنگل‌داری و جنگل‌بانان | بازرسان و ممیزان اموال دولتی | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | کارشناسان مدیریت پروژه | کارشناسان پایداری و توسعه پایدار | برنامه‌ریزان شهری و منطقه‌ای | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>انجام مطالعات امکان‌سنجی فنی و تحلیل‌های هزینه-فایده پروژه‌های اصلاح زیست‌محیطی | ارزیابی کمی و کیفی مخاطرات آلودگی خاک، آب و هوا بر سلامت انسان و محیط | برنامه‌ریزی و نظارت بر عملیات پاک‌سازی سایت مطابق با الزامات و استانداردهای قانونی | طراحی و نظارت بر اجرای طرح‌های تصفیه و پالایش منابع آب سطحی و زیرزمینی | نظارت فنی بر عملیات تخریب ایمن سازه‌ها و جمع‌آوری پسماندهای ساختمانی | هماهنگی و نظارت بر فرآیندهای بی‌خطرسازی و دفن پسماندهای ویژه و خطرناک | برآورد هزینه‌ها، کنترل بودجه و جذب منابع مالی برای پروژه‌های بازسازی اراضی | بازرسی‌های میدانی از کارگاه‌ها جهت سنجش انتشار آلودگی و پایش پیشرفت عملیات | تهیه اسناد فنی، گزارش‌های ممیزی و پیگیری اخذ مجوزهای قانونی از مراجع ذی‌صلاح | مذاکره و انعقاد قرارداد با پیمانکاران تخصصی تصفیه، خاک‌برداری و دفع ضایعات</t>
+          <t>انجام مطالعات امکان‌سنجی یا هزینه‌فایده برای پروژه‌های پاک‌سازی محیط‌زیستی. | انجام ارزیابی‌های کمّی ریسک برای سلامت انسان، محیط‌زیست یا سایر مخاطرات. | هماهنگی فعالیت‌های میدانی پروژه‌های پاک‌سازی یا احیای محیط‌زیستی برای اطمینان از رعایت قوانین، استانداردها، مقررات یا سایر الزامات محیط‌زیستی. | هماهنگی دفع پسماند خطرناک. | طراحی یا انجام مطالعات احیای محیط‌زیست. | طراحی یا اجرای اقداماتی برای بهبود کیفیت آب، هوا و خاک محل‌های آزمایش نظامی، اراضی معدنی متروکه یا سایر محل‌های آلوده. | طراحی یا اجرای برنامه‌های تخریب سازه‌ای و برداشت نخاله. | طراحی یا اجرای برنامه‌های پاک‌سازی آب‌های سطحی یا زیرزمینی. | تدوین یا اجرای برنامه‌های بازگرداندن پوشش گیاهی در اراضی قهوه‌ای (آلوده متروکه). | تدوین یا اجرای برنامه‌های بازآفرینی پایدار اراضی قهوه‌ای برای اطمینان از احیای پهنه گسترده‌تر از راه حفاظت محیط‌زیستی یا ایجاد منافع اقتصادی و اجتماعی. | برآورد هزینه‌های پاک‌سازی و احیای محیط‌زیستی پروژه‌های بازتوسعه اراضی. | شناسایی منابع تأمین مالی پروژه و درخواست آن. | شناسایی منابع آلودگی محیط‌زیستی. | بازرسی محل‌ها برای ارزیابی آسیب محیط‌زیستی یا پایش پیشرفت پاک‌سازی. | نگهداری سوابق تصمیم‌ها، اقدامات و پیشرفت پروژه‌های بازتوسعه محیط‌زیستی. | مذاکره درباره قراردادهای خدمات یا مواد مورد نیاز پاک‌سازی محیط‌زیستی. | برنامه‌ریزی یا اجرای پروژه‌های بازتوسعه اراضی قهوه‌ای برای تضمین ایمنی، کیفیت و انطباق با استانداردها یا الزامات مربوطه. | تهیه و ارائه درخواست مجوز برای پروژه‌های تخریب، پاک‌سازی، احیا یا ساخت. | تهیه گزارش‌ها یا ارائه‌ها برای انتقال نیازها، وضعیت یا پیشرفت بازتوسعه اراضی قهوه‌ای. | ارائه شهادت کارشناسی در موضوعاتی مانند آلودگی خاک، هوا یا آب و اقدامات پاک‌سازی مرتبط با آن. | ارائه آموزش درباره رویه‌ها و فناوری‌های پاک‌سازی مواد یا پسماند خطرناک. | بازبینی یا ارزیابی طرح‌های تأسیسات تصفیه یا دفع آلاینده‌ها. | بازبینی یا ارزیابی پیشنهادهای پروژه پاک‌سازی محیط‌زیستی.</t>
         </is>
       </c>
     </row>
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | زبان انگلیسی | مدیریت و امور اداری | هنرهای تجسمی و نمایشی | ارتباطات و رسانه | امور اداری و دفتری | امور اداری و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مدیریت و اداره | هنرهای زیبا | ارتباطات و رسانه | اداری | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | استدلال استقرایی | دید نزدیک | مرتب‌سازی اطلاعات | سیالی ذهنی | ابتکار و اصالت | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نمایندگان فروش آگهی‌های تبلیغاتی | مدیران تبلیغات و روابط تجاری | مدیران هنری | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | مسئولان جذب حامیان مالی | مدیران جذب منابع و حامیان مالی | کارشناسان تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | هماهنگ‌کنندگان همایش‌ها، کنفرانس‌ها و رویدادها | مشاوران مالی شخصی | تهیه‌کنندگان و کارگردانان | مدیران روابط عمومی | کارشناسان روابط عمومی | مشاوران و نمایندگان فروش املاک | مدیران فروش | نمایندگان فروش خدمات بازرگانی | کارگزاران بورس، کالا و اوراق بهادار | مسئولان انتخاب بازیگر و استعدادیابی | بازاریابان تلفنی | نویسندگان و پدیدآورندگان</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | مدیران هنری | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | کارشناسان جذب منابع مالی و حامی | مدیران جذب منابع مالی و حامیان | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مشاوران مالی فردی | تهیه‌کنندگان و کارگردانان | مدیران روابط عمومی | کارشناسان روابط عمومی | مشاوران و کارشناسان فروش املاک | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | مسئولان انتخاب بازیگر و استعدادیابی | کارشناسان بازاریابی تلفنی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>مذاکره با کارفرمایان، تهیه‌کنندگان، باشگاه‌ها و نهادهای صنفی درباره تعهدات قراردادی موکلان | بازاریابی، توسعه برند شخصی و تدوین راهبردهای موفقیت حرفه‌ای برای موکلان | مدیریت امور مالی، مالیاتی و تجاری موکلان از جمله قراردادهای اسپانسری و تبلیغاتی | هماهنگی و برنامه‌ریزی جلسات، اجراها، رویدادها، نشست‌های تبلیغاتی و تقویم کاری | هماهنگی محل اقامت، امور سفر، تشریفات و تأمین نیازمندی‌های رفاهی موکلان | پیگیری وصول دستمزدها، مطالبات مالی، کارمزدها و حق‌الوکاله‌ها طبق قرارداد | ارسال نمونه آثار، رزومه و اقلام تبلیغاتی برای جلب حامیان مالی و فرصت‌های جدید | بررسی و اعتبارسنجی مکان‌های اجرا، تجهیزات فنی و استانداردهای سالن‌ها و اماکن | انجام مصاحبه‌ها و آزمون‌های استعدادیابی جهت ارزیابی و پذیرش موکلان جدید | پیگیری وضعیت قراردادها، روند بازار و فرصت‌های جدید حوزه ورزش و هنر</t>
+          <t>ارائه مشاوره به مشتریان در امور مالی و حقوقی، مانند سرمایه‌گذاری و مالیات. | ترتیب دادن جلسات درباره موضوعات مرتبط با مشتریان. | دریافت حق‌الزحمه، کارمزد یا سایر پرداخت‌ها، بر پایه شرایط قرارداد. | برگزاری آزمون هنری یا مصاحبه برای ارزیابی مشتریان بالقوه. | رایزنی با مشتریان برای تدوین راهبردهای شغلی آنان و تشریح اقدامات انجام‌شده از سوی ایشان. | ایجاد ارتباط با افراد و سازمان‌ها و به‌کارگیری راهبردها و فنون مؤثر برای تضمین موفقیت مشتریان. | به‌کارگیری مربیان یا مدرسان برای مشاوره به مشتریان در موضوعات اجرایی، مانند فنون تمرین یا شیوه ارائه اجرا. | آگاه ماندن از روندها و معاملات صنعت. | مدیریت امور تجاری و مالی مشتریان، مانند ترتیب دادن سفر و اقامت، فروش بلیت و هدایت فعالیت‌های بازاریابی و تبلیغات. | مذاکره با مدیران، برگزارکنندگان، مقامات صنفی و سایر افراد درباره حقوق و تعهدات قراردادی مشتریان. | کسب اطلاعات درباره امکانات، تجهیزات و محل اقامت مربوط به اجرا یا بازرسی آن‌ها برای اطمینان از انطباق با مشخصات. | تهیه صورت‌حساب‌های دوره‌ای برای مشتریان. | زمان‌بندی برنامه‌های تبلیغاتی یا اجرایی مشتریان. | ارسال نمونه آثار مشتریان و سایر مواد تبلیغاتی به کارفرمایان بالقوه برای دریافت فرصت آزمون هنری، حمایت مالی یا قرارداد تبلیغاتی.</t>
         </is>
       </c>
     </row>
